--- a/research/traditional_assets/database/data/romania/romania_household_products.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_household_products.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.123</v>
+        <v>-0.173</v>
       </c>
       <c r="G2">
-        <v>-0.2978303747534516</v>
+        <v>-0.3829787234042554</v>
       </c>
       <c r="H2">
-        <v>-0.2978303747534516</v>
+        <v>-0.3829787234042554</v>
       </c>
       <c r="I2">
-        <v>-0.2583826429980276</v>
+        <v>-0.5283687943262412</v>
       </c>
       <c r="J2">
-        <v>-0.2583826429980276</v>
+        <v>-0.5283687943262412</v>
       </c>
       <c r="K2">
-        <v>-1.35</v>
+        <v>-1.51</v>
       </c>
       <c r="L2">
-        <v>-0.2662721893491125</v>
+        <v>-0.5354609929078015</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-2.331125827814569</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,73 +627,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>3.52</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>0.046</v>
+        <v>0.004</v>
       </c>
       <c r="V2">
-        <v>0.00886319845857418</v>
+        <v>0.001041666666666667</v>
       </c>
       <c r="W2">
-        <v>0.3013392857142857</v>
+        <v>1.006666666666667</v>
       </c>
       <c r="X2">
-        <v>0.1626930376862125</v>
+        <v>0.3077846279069223</v>
       </c>
       <c r="Y2">
-        <v>0.1386462480280732</v>
+        <v>0.6988820387597443</v>
       </c>
       <c r="Z2">
-        <v>-2.481644640234948</v>
+        <v>0.3986429177268872</v>
       </c>
       <c r="AA2">
-        <v>0.6412139011257952</v>
+        <v>-0.2106304778060503</v>
       </c>
       <c r="AB2">
-        <v>0.08722211214338307</v>
+        <v>0.144710971317727</v>
       </c>
       <c r="AC2">
-        <v>0.5539917889824122</v>
+        <v>-0.3553414491237773</v>
       </c>
       <c r="AD2">
-        <v>8.619999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>8.619999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="AG2">
-        <v>8.574</v>
+        <v>8.606</v>
       </c>
       <c r="AH2">
-        <v>0.6241853729181752</v>
+        <v>0.691566265060241</v>
       </c>
       <c r="AI2">
-        <v>1.210674157303371</v>
+        <v>3.727272727272728</v>
       </c>
       <c r="AJ2">
-        <v>0.6229293809938972</v>
+        <v>0.6914671380363169</v>
       </c>
       <c r="AK2">
-        <v>1.212044105173876</v>
+        <v>3.732003469210754</v>
       </c>
       <c r="AL2">
-        <v>0.005</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AN2">
-        <v>-7.908256880733943</v>
+        <v>-6.674418604651162</v>
       </c>
       <c r="AO2">
-        <v>-262</v>
+        <v>-165.5555555555556</v>
       </c>
       <c r="AP2">
-        <v>-7.866055045871559</v>
+        <v>-6.671317829457364</v>
+      </c>
+      <c r="AQ2">
+        <v>-165.5555555555556</v>
       </c>
     </row>
     <row r="3">
@@ -713,34 +719,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.123</v>
+        <v>-0.173</v>
       </c>
       <c r="G3">
-        <v>-0.2978303747534516</v>
+        <v>-0.3829787234042554</v>
       </c>
       <c r="H3">
-        <v>-0.2978303747534516</v>
+        <v>-0.3829787234042554</v>
       </c>
       <c r="I3">
-        <v>-0.2583826429980276</v>
+        <v>-0.5283687943262412</v>
       </c>
       <c r="J3">
-        <v>-0.2583826429980276</v>
+        <v>-0.5283687943262412</v>
       </c>
       <c r="K3">
-        <v>-1.35</v>
+        <v>-1.51</v>
       </c>
       <c r="L3">
-        <v>-0.2662721893491125</v>
+        <v>-0.5354609929078015</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>3.52</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-2.331125827814569</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,73 +758,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>3.52</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0.046</v>
+        <v>0.004</v>
       </c>
       <c r="V3">
-        <v>0.00886319845857418</v>
+        <v>0.001041666666666667</v>
       </c>
       <c r="W3">
-        <v>0.3013392857142857</v>
+        <v>1.006666666666667</v>
       </c>
       <c r="X3">
-        <v>0.1626930376862125</v>
+        <v>0.3077846279069223</v>
       </c>
       <c r="Y3">
-        <v>0.1386462480280732</v>
+        <v>0.6988820387597443</v>
       </c>
       <c r="Z3">
-        <v>-2.481644640234948</v>
+        <v>0.3986429177268872</v>
       </c>
       <c r="AA3">
-        <v>0.6412139011257952</v>
+        <v>-0.2106304778060503</v>
       </c>
       <c r="AB3">
-        <v>0.08722211214338307</v>
+        <v>0.144710971317727</v>
       </c>
       <c r="AC3">
-        <v>0.5539917889824122</v>
+        <v>-0.3553414491237773</v>
       </c>
       <c r="AD3">
-        <v>8.619999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>8.619999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="AG3">
-        <v>8.574</v>
+        <v>8.606</v>
       </c>
       <c r="AH3">
-        <v>0.6241853729181752</v>
+        <v>0.691566265060241</v>
       </c>
       <c r="AI3">
-        <v>1.210674157303371</v>
+        <v>3.727272727272728</v>
       </c>
       <c r="AJ3">
-        <v>0.6229293809938972</v>
+        <v>0.6914671380363169</v>
       </c>
       <c r="AK3">
-        <v>1.212044105173876</v>
+        <v>3.732003469210754</v>
       </c>
       <c r="AL3">
-        <v>0.005</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AN3">
-        <v>-7.908256880733943</v>
+        <v>-6.674418604651162</v>
       </c>
       <c r="AO3">
-        <v>-262</v>
+        <v>-165.5555555555556</v>
       </c>
       <c r="AP3">
-        <v>-7.866055045871559</v>
+        <v>-6.671317829457364</v>
+      </c>
+      <c r="AQ3">
+        <v>-165.5555555555556</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/romania/romania_household_products.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_household_products.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.173</v>
+        <v>-0.232</v>
       </c>
       <c r="G2">
-        <v>-0.3829787234042554</v>
+        <v>-0.5727699530516432</v>
       </c>
       <c r="H2">
-        <v>-0.3829787234042554</v>
+        <v>-0.5727699530516432</v>
       </c>
       <c r="I2">
-        <v>-0.5283687943262412</v>
+        <v>-0.6854460093896714</v>
       </c>
       <c r="J2">
-        <v>-0.5283687943262412</v>
+        <v>-0.6854460093896714</v>
       </c>
       <c r="K2">
-        <v>-1.51</v>
+        <v>-1.47</v>
       </c>
       <c r="L2">
-        <v>-0.5354609929078015</v>
+        <v>-0.6901408450704225</v>
       </c>
       <c r="M2">
-        <v>3.52</v>
+        <v>0.013</v>
       </c>
       <c r="N2">
-        <v>0.9166666666666667</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="O2">
-        <v>-2.331125827814569</v>
+        <v>-0.008843537414965985</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +627,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>3.52</v>
+        <v>0.013</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>0.004</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="V2">
-        <v>0.001041666666666667</v>
+        <v>0.003461538461538461</v>
       </c>
       <c r="W2">
-        <v>1.006666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="X2">
-        <v>0.3077846279069223</v>
+        <v>0.2491712970970118</v>
       </c>
       <c r="Y2">
-        <v>0.6988820387597443</v>
+        <v>-0.01583796376367846</v>
       </c>
       <c r="Z2">
-        <v>0.3986429177268872</v>
+        <v>0.9236773633998266</v>
       </c>
       <c r="AA2">
-        <v>-0.2106304778060503</v>
+        <v>-0.6331309627059845</v>
       </c>
       <c r="AB2">
-        <v>0.144710971317727</v>
+        <v>0.1055687207717264</v>
       </c>
       <c r="AC2">
-        <v>-0.3553414491237773</v>
+        <v>-0.7386996834777109</v>
       </c>
       <c r="AD2">
-        <v>8.609999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>8.609999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AG2">
-        <v>8.606</v>
+        <v>9.211</v>
       </c>
       <c r="AH2">
-        <v>0.691566265060241</v>
+        <v>0.7800338409475466</v>
       </c>
       <c r="AI2">
-        <v>3.727272727272728</v>
+        <v>9.604166666666659</v>
       </c>
       <c r="AJ2">
-        <v>0.6914671380363169</v>
+        <v>0.7798662263991195</v>
       </c>
       <c r="AK2">
-        <v>3.732003469210754</v>
+        <v>9.685594111461615</v>
       </c>
       <c r="AL2">
-        <v>0.008999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="AM2">
-        <v>0.008999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="AN2">
-        <v>-6.674418604651162</v>
+        <v>-7.619834710743802</v>
       </c>
       <c r="AO2">
-        <v>-165.5555555555556</v>
+        <v>-121.6666666666667</v>
       </c>
       <c r="AP2">
-        <v>-6.671317829457364</v>
+        <v>-7.612396694214876</v>
       </c>
       <c r="AQ2">
-        <v>-165.5555555555556</v>
+        <v>-121.6666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -719,34 +719,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.173</v>
+        <v>-0.232</v>
       </c>
       <c r="G3">
-        <v>-0.3829787234042554</v>
+        <v>-0.5727699530516432</v>
       </c>
       <c r="H3">
-        <v>-0.3829787234042554</v>
+        <v>-0.5727699530516432</v>
       </c>
       <c r="I3">
-        <v>-0.5283687943262412</v>
+        <v>-0.6854460093896714</v>
       </c>
       <c r="J3">
-        <v>-0.5283687943262412</v>
+        <v>-0.6854460093896714</v>
       </c>
       <c r="K3">
-        <v>-1.51</v>
+        <v>-1.47</v>
       </c>
       <c r="L3">
-        <v>-0.5354609929078015</v>
+        <v>-0.6901408450704225</v>
       </c>
       <c r="M3">
-        <v>3.52</v>
+        <v>0.013</v>
       </c>
       <c r="N3">
-        <v>0.9166666666666667</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="O3">
-        <v>-2.331125827814569</v>
+        <v>-0.008843537414965985</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +758,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>3.52</v>
+        <v>0.013</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>0.004</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="V3">
-        <v>0.001041666666666667</v>
+        <v>0.003461538461538461</v>
       </c>
       <c r="W3">
-        <v>1.006666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="X3">
-        <v>0.3077846279069223</v>
+        <v>0.2491712970970118</v>
       </c>
       <c r="Y3">
-        <v>0.6988820387597443</v>
+        <v>-0.01583796376367846</v>
       </c>
       <c r="Z3">
-        <v>0.3986429177268872</v>
+        <v>0.9236773633998266</v>
       </c>
       <c r="AA3">
-        <v>-0.2106304778060503</v>
+        <v>-0.6331309627059845</v>
       </c>
       <c r="AB3">
-        <v>0.144710971317727</v>
+        <v>0.1055687207717264</v>
       </c>
       <c r="AC3">
-        <v>-0.3553414491237773</v>
+        <v>-0.7386996834777109</v>
       </c>
       <c r="AD3">
-        <v>8.609999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>8.609999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AG3">
-        <v>8.606</v>
+        <v>9.211</v>
       </c>
       <c r="AH3">
-        <v>0.691566265060241</v>
+        <v>0.7800338409475466</v>
       </c>
       <c r="AI3">
-        <v>3.727272727272728</v>
+        <v>9.604166666666659</v>
       </c>
       <c r="AJ3">
-        <v>0.6914671380363169</v>
+        <v>0.7798662263991195</v>
       </c>
       <c r="AK3">
-        <v>3.732003469210754</v>
+        <v>9.685594111461615</v>
       </c>
       <c r="AL3">
-        <v>0.008999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="AM3">
-        <v>0.008999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="AN3">
-        <v>-6.674418604651162</v>
+        <v>-7.619834710743802</v>
       </c>
       <c r="AO3">
-        <v>-165.5555555555556</v>
+        <v>-121.6666666666667</v>
       </c>
       <c r="AP3">
-        <v>-6.671317829457364</v>
+        <v>-7.612396694214876</v>
       </c>
       <c r="AQ3">
-        <v>-165.5555555555556</v>
+        <v>-121.6666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/romania/romania_household_products.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_household_products.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09495354517041182</v>
+        <v>0.09483941949813918</v>
       </c>
       <c r="C2">
-        <v>7.989504021035825</v>
+        <v>7.924105713184824</v>
       </c>
       <c r="D2">
-        <v>7.008504021035825</v>
+        <v>7.018405713184825</v>
       </c>
       <c r="E2">
-        <v>-3.859999999999999</v>
+        <v>-3.7847</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.07529999999999999</v>
       </c>
       <c r="G2">
         <v>0.981</v>
@@ -1445,28 +1445,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.00378759</v>
       </c>
       <c r="N2">
-        <v>0.7180000000000002</v>
+        <v>0.7142124100000002</v>
       </c>
       <c r="O2">
-        <v>0.11488</v>
+        <v>0.1142739856</v>
       </c>
       <c r="P2">
-        <v>0.6031200000000001</v>
+        <v>0.5999384244000002</v>
       </c>
       <c r="Q2">
-        <v>0.90012</v>
+        <v>0.8969384244000003</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09495354517041182</v>
+        <v>0.09537060555367594</v>
       </c>
       <c r="T2">
-        <v>0.6766170509100436</v>
+        <v>0.6823580440692805</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>189.5664525463422</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09483941949813918</v>
+        <v>0.09472529382586652</v>
       </c>
       <c r="C3">
-        <v>7.924105713184824</v>
+        <v>7.858735423358799</v>
       </c>
       <c r="D3">
-        <v>7.018405713184825</v>
+        <v>7.028335423358798</v>
       </c>
       <c r="E3">
-        <v>-3.7847</v>
+        <v>-3.7094</v>
       </c>
       <c r="F3">
-        <v>0.07529999999999999</v>
+        <v>0.1506</v>
       </c>
       <c r="G3">
         <v>0.981</v>
@@ -1527,28 +1527,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M3">
-        <v>0.00378759</v>
+        <v>0.007575179999999999</v>
       </c>
       <c r="N3">
-        <v>0.7142124100000002</v>
+        <v>0.7104248200000002</v>
       </c>
       <c r="O3">
-        <v>0.1142739856</v>
+        <v>0.1136679712</v>
       </c>
       <c r="P3">
-        <v>0.5999384244000002</v>
+        <v>0.5967568488000001</v>
       </c>
       <c r="Q3">
-        <v>0.8969384244000003</v>
+        <v>0.8937568488000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09537060555367594</v>
+        <v>0.09579617737333318</v>
       </c>
       <c r="T3">
-        <v>0.6823580440692805</v>
+        <v>0.6882162003542158</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>189.5664525463422</v>
+        <v>94.7832262731711</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09472529382586652</v>
+        <v>0.09461116815359384</v>
       </c>
       <c r="C4">
-        <v>7.858735423358799</v>
+        <v>7.793393270646777</v>
       </c>
       <c r="D4">
-        <v>7.028335423358798</v>
+        <v>7.038293270646776</v>
       </c>
       <c r="E4">
-        <v>-3.7094</v>
+        <v>-3.6341</v>
       </c>
       <c r="F4">
-        <v>0.1506</v>
+        <v>0.2259</v>
       </c>
       <c r="G4">
         <v>0.981</v>
@@ -1609,28 +1609,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M4">
-        <v>0.007575179999999999</v>
+        <v>0.01136277</v>
       </c>
       <c r="N4">
-        <v>0.7104248200000002</v>
+        <v>0.7066372300000002</v>
       </c>
       <c r="O4">
-        <v>0.1136679712</v>
+        <v>0.1130619568</v>
       </c>
       <c r="P4">
-        <v>0.5967568488000001</v>
+        <v>0.5935752732000001</v>
       </c>
       <c r="Q4">
-        <v>0.8937568488000001</v>
+        <v>0.8905752732000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09579617737333318</v>
+        <v>0.09623052386968438</v>
       </c>
       <c r="T4">
-        <v>0.6882162003542158</v>
+        <v>0.6941951433666756</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>94.7832262731711</v>
+        <v>63.18881751544741</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09461116815359384</v>
+        <v>0.09449704248132118</v>
       </c>
       <c r="C5">
-        <v>7.793393270646777</v>
+        <v>7.728079374813651</v>
       </c>
       <c r="D5">
-        <v>7.038293270646776</v>
+        <v>7.04827937481365</v>
       </c>
       <c r="E5">
-        <v>-3.6341</v>
+        <v>-3.558799999999999</v>
       </c>
       <c r="F5">
-        <v>0.2259</v>
+        <v>0.3012</v>
       </c>
       <c r="G5">
         <v>0.981</v>
@@ -1691,28 +1691,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M5">
-        <v>0.01136277</v>
+        <v>0.01515036</v>
       </c>
       <c r="N5">
-        <v>0.7066372300000002</v>
+        <v>0.7028496400000002</v>
       </c>
       <c r="O5">
-        <v>0.1130619568</v>
+        <v>0.1124559424</v>
       </c>
       <c r="P5">
-        <v>0.5935752732000001</v>
+        <v>0.5903936976000002</v>
       </c>
       <c r="Q5">
-        <v>0.8905752732000001</v>
+        <v>0.8873936976000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09623052386968438</v>
+        <v>0.09667391925137624</v>
       </c>
       <c r="T5">
-        <v>0.6941951433666756</v>
+        <v>0.7002986476918951</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>63.18881751544741</v>
+        <v>47.39161313658555</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09449704248132118</v>
+        <v>0.09438291680904853</v>
       </c>
       <c r="C6">
-        <v>7.728079374813651</v>
+        <v>7.662793856304981</v>
       </c>
       <c r="D6">
-        <v>7.04827937481365</v>
+        <v>7.058293856304982</v>
       </c>
       <c r="E6">
-        <v>-3.558799999999999</v>
+        <v>-3.483499999999999</v>
       </c>
       <c r="F6">
-        <v>0.3012</v>
+        <v>0.3765</v>
       </c>
       <c r="G6">
         <v>0.981</v>
@@ -1773,28 +1773,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M6">
-        <v>0.01515036</v>
+        <v>0.01893795</v>
       </c>
       <c r="N6">
-        <v>0.7028496400000002</v>
+        <v>0.6990620500000002</v>
       </c>
       <c r="O6">
-        <v>0.1124559424</v>
+        <v>0.111849928</v>
       </c>
       <c r="P6">
-        <v>0.5903936976000002</v>
+        <v>0.5872121220000002</v>
       </c>
       <c r="Q6">
-        <v>0.8873936976000001</v>
+        <v>0.8842121220000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09667391925137624</v>
+        <v>0.09712664927268266</v>
       </c>
       <c r="T6">
-        <v>0.7002986476918951</v>
+        <v>0.706530646845014</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>47.39161313658555</v>
+        <v>37.91329050926844</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09438291680904853</v>
+        <v>0.09426879113677587</v>
       </c>
       <c r="C7">
-        <v>7.662793856304981</v>
+        <v>7.597536836251846</v>
       </c>
       <c r="D7">
-        <v>7.058293856304982</v>
+        <v>7.068336836251846</v>
       </c>
       <c r="E7">
-        <v>-3.483499999999999</v>
+        <v>-3.408199999999999</v>
       </c>
       <c r="F7">
-        <v>0.3765</v>
+        <v>0.4518</v>
       </c>
       <c r="G7">
         <v>0.981</v>
@@ -1855,28 +1855,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M7">
-        <v>0.01893795</v>
+        <v>0.02272554</v>
       </c>
       <c r="N7">
-        <v>0.6990620500000002</v>
+        <v>0.6952744600000001</v>
       </c>
       <c r="O7">
-        <v>0.111849928</v>
+        <v>0.1112439136</v>
       </c>
       <c r="P7">
-        <v>0.5872121220000002</v>
+        <v>0.5840305464000002</v>
       </c>
       <c r="Q7">
-        <v>0.8842121220000001</v>
+        <v>0.8810305464000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09712664927268266</v>
+        <v>0.09758901184763391</v>
       </c>
       <c r="T7">
-        <v>0.706530646845014</v>
+        <v>0.712895241724795</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.91329050926844</v>
+        <v>31.5944087577237</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09426879113677587</v>
+        <v>0.09415466546450321</v>
       </c>
       <c r="C8">
-        <v>7.597536836251847</v>
+        <v>7.532308436475707</v>
       </c>
       <c r="D8">
-        <v>7.068336836251846</v>
+        <v>7.078408436475707</v>
       </c>
       <c r="E8">
-        <v>-3.408199999999999</v>
+        <v>-3.3329</v>
       </c>
       <c r="F8">
-        <v>0.4517999999999999</v>
+        <v>0.5270999999999999</v>
       </c>
       <c r="G8">
         <v>0.981</v>
@@ -1937,28 +1937,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M8">
-        <v>0.02272554</v>
+        <v>0.02651312999999999</v>
       </c>
       <c r="N8">
-        <v>0.6952744600000001</v>
+        <v>0.6914868700000002</v>
       </c>
       <c r="O8">
-        <v>0.1112439136</v>
+        <v>0.1106378992</v>
       </c>
       <c r="P8">
-        <v>0.5840305464000002</v>
+        <v>0.5808489708000002</v>
       </c>
       <c r="Q8">
-        <v>0.8810305464000001</v>
+        <v>0.8778489708000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09758901184763391</v>
+        <v>0.09806131770376689</v>
       </c>
       <c r="T8">
-        <v>0.712895241724795</v>
+        <v>0.7193967096127432</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.5944087577237</v>
+        <v>27.08092179233461</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0941546654645032</v>
+        <v>0.09404053979223057</v>
       </c>
       <c r="C9">
-        <v>7.532308436475708</v>
+        <v>7.467108779493349</v>
       </c>
       <c r="D9">
-        <v>7.078408436475708</v>
+        <v>7.088508779493349</v>
       </c>
       <c r="E9">
-        <v>-3.3329</v>
+        <v>-3.2576</v>
       </c>
       <c r="F9">
-        <v>0.5271</v>
+        <v>0.6023999999999999</v>
       </c>
       <c r="G9">
         <v>0.981</v>
@@ -2019,28 +2019,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M9">
-        <v>0.02651313</v>
+        <v>0.03030072</v>
       </c>
       <c r="N9">
-        <v>0.6914868700000002</v>
+        <v>0.6876992800000002</v>
       </c>
       <c r="O9">
-        <v>0.1106378992</v>
+        <v>0.1100318848</v>
       </c>
       <c r="P9">
-        <v>0.5808489708000002</v>
+        <v>0.5776673952000002</v>
       </c>
       <c r="Q9">
-        <v>0.8778489708000001</v>
+        <v>0.8746673952000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09806131770376689</v>
+        <v>0.09854389107851147</v>
       </c>
       <c r="T9">
-        <v>0.7193967096127432</v>
+        <v>0.7260395137591251</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.0809217923346</v>
+        <v>23.69580656829278</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09404053979223057</v>
+        <v>0.09392641411995789</v>
       </c>
       <c r="C10">
-        <v>7.467108779493349</v>
+        <v>7.401937988521848</v>
       </c>
       <c r="D10">
-        <v>7.088508779493349</v>
+        <v>7.098637988521848</v>
       </c>
       <c r="E10">
-        <v>-3.2576</v>
+        <v>-3.1823</v>
       </c>
       <c r="F10">
-        <v>0.6023999999999999</v>
+        <v>0.6777</v>
       </c>
       <c r="G10">
         <v>0.981</v>
@@ -2101,28 +2101,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M10">
-        <v>0.03030072</v>
+        <v>0.03408831</v>
       </c>
       <c r="N10">
-        <v>0.6876992800000002</v>
+        <v>0.6839116900000002</v>
       </c>
       <c r="O10">
-        <v>0.1100318848</v>
+        <v>0.1094258704</v>
       </c>
       <c r="P10">
-        <v>0.5776673952000002</v>
+        <v>0.5744858196000001</v>
       </c>
       <c r="Q10">
-        <v>0.8746673952000001</v>
+        <v>0.8714858196000002</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09854389107851147</v>
+        <v>0.09903707046149218</v>
       </c>
       <c r="T10">
-        <v>0.7260395137591251</v>
+        <v>0.7328283136010318</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.69580656829278</v>
+        <v>21.0629391718158</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09392641411995789</v>
+        <v>0.09381228844768523</v>
       </c>
       <c r="C11">
-        <v>7.401937988521848</v>
+        <v>7.33679618748357</v>
       </c>
       <c r="D11">
-        <v>7.098637988521848</v>
+        <v>7.10879618748357</v>
       </c>
       <c r="E11">
-        <v>-3.1823</v>
+        <v>-3.106999999999999</v>
       </c>
       <c r="F11">
-        <v>0.6777</v>
+        <v>0.7529999999999999</v>
       </c>
       <c r="G11">
         <v>0.981</v>
@@ -2183,28 +2183,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M11">
-        <v>0.03408831</v>
+        <v>0.03787589999999999</v>
       </c>
       <c r="N11">
-        <v>0.6839116900000002</v>
+        <v>0.6801241000000002</v>
       </c>
       <c r="O11">
-        <v>0.1094258704</v>
+        <v>0.108819856</v>
       </c>
       <c r="P11">
-        <v>0.5744858196000001</v>
+        <v>0.5713042440000002</v>
       </c>
       <c r="Q11">
-        <v>0.8714858196000002</v>
+        <v>0.8683042440000002</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09903707046149218</v>
+        <v>0.09954120938631691</v>
       </c>
       <c r="T11">
-        <v>0.7328283136010318</v>
+        <v>0.7397679756616476</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.0629391718158</v>
+        <v>18.95664525463422</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09381228844768523</v>
+        <v>0.09369816277541257</v>
       </c>
       <c r="C12">
-        <v>7.33679618748357</v>
+        <v>7.27168350101124</v>
       </c>
       <c r="D12">
-        <v>7.10879618748357</v>
+        <v>7.118983501011239</v>
       </c>
       <c r="E12">
-        <v>-3.106999999999999</v>
+        <v>-3.031699999999999</v>
       </c>
       <c r="F12">
-        <v>0.753</v>
+        <v>0.8282999999999999</v>
       </c>
       <c r="G12">
         <v>0.981</v>
@@ -2265,28 +2265,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M12">
-        <v>0.0378759</v>
+        <v>0.04166349</v>
       </c>
       <c r="N12">
-        <v>0.6801241000000002</v>
+        <v>0.6763365100000002</v>
       </c>
       <c r="O12">
-        <v>0.108819856</v>
+        <v>0.1082138416</v>
       </c>
       <c r="P12">
-        <v>0.5713042440000002</v>
+        <v>0.5681226684000001</v>
       </c>
       <c r="Q12">
-        <v>0.8683042440000002</v>
+        <v>0.8651226684000002</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09954120938631691</v>
+        <v>0.1000566772757445</v>
       </c>
       <c r="T12">
-        <v>0.7397679756616476</v>
+        <v>0.7468635851842998</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.95664525463422</v>
+        <v>17.23331386784929</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09369816277541257</v>
+        <v>0.09358403710313992</v>
       </c>
       <c r="C13">
-        <v>7.27168350101124</v>
+        <v>7.206600054453022</v>
       </c>
       <c r="D13">
-        <v>7.118983501011239</v>
+        <v>7.129200054453023</v>
       </c>
       <c r="E13">
-        <v>-3.031699999999999</v>
+        <v>-2.956399999999999</v>
       </c>
       <c r="F13">
-        <v>0.8282999999999999</v>
+        <v>0.9035999999999998</v>
       </c>
       <c r="G13">
         <v>0.981</v>
@@ -2347,28 +2347,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M13">
-        <v>0.04166349</v>
+        <v>0.04545107999999999</v>
       </c>
       <c r="N13">
-        <v>0.6763365100000002</v>
+        <v>0.6725489200000002</v>
       </c>
       <c r="O13">
-        <v>0.1082138416</v>
+        <v>0.1076078272</v>
       </c>
       <c r="P13">
-        <v>0.5681226684000001</v>
+        <v>0.5649410928000002</v>
       </c>
       <c r="Q13">
-        <v>0.8651226684000002</v>
+        <v>0.8619410928000002</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1000566772757445</v>
+        <v>0.1005838603444772</v>
       </c>
       <c r="T13">
-        <v>0.7468635851842998</v>
+        <v>0.7541204585597395</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.23331386784929</v>
+        <v>15.79720437886185</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09358403710313992</v>
+        <v>0.09346991143086726</v>
       </c>
       <c r="C14">
-        <v>7.206600054453022</v>
+        <v>7.141545973877684</v>
       </c>
       <c r="D14">
-        <v>7.129200054453023</v>
+        <v>7.139445973877685</v>
       </c>
       <c r="E14">
-        <v>-2.956399999999999</v>
+        <v>-2.8811</v>
       </c>
       <c r="F14">
-        <v>0.9035999999999998</v>
+        <v>0.9789</v>
       </c>
       <c r="G14">
         <v>0.981</v>
@@ -2429,28 +2429,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M14">
-        <v>0.04545107999999999</v>
+        <v>0.04923867</v>
       </c>
       <c r="N14">
-        <v>0.6725489200000002</v>
+        <v>0.6687613300000002</v>
       </c>
       <c r="O14">
-        <v>0.1076078272</v>
+        <v>0.1070018128</v>
       </c>
       <c r="P14">
-        <v>0.5649410928000002</v>
+        <v>0.5617595172000002</v>
       </c>
       <c r="Q14">
-        <v>0.8619410928000002</v>
+        <v>0.8587595172000002</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1005838603444772</v>
+        <v>0.1011231625642152</v>
       </c>
       <c r="T14">
-        <v>0.7541204585597395</v>
+        <v>0.7615441566104768</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.79720437886185</v>
+        <v>14.58203481125709</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09346991143086726</v>
+        <v>0.0933557857585946</v>
       </c>
       <c r="C15">
-        <v>7.141545973877684</v>
+        <v>7.07652138607976</v>
       </c>
       <c r="D15">
-        <v>7.139445973877685</v>
+        <v>7.149721386079759</v>
       </c>
       <c r="E15">
-        <v>-2.8811</v>
+        <v>-2.8058</v>
       </c>
       <c r="F15">
-        <v>0.9789</v>
+        <v>1.0542</v>
       </c>
       <c r="G15">
         <v>0.981</v>
@@ -2511,28 +2511,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M15">
-        <v>0.04923867</v>
+        <v>0.05302626</v>
       </c>
       <c r="N15">
-        <v>0.6687613300000002</v>
+        <v>0.6649737400000002</v>
       </c>
       <c r="O15">
-        <v>0.1070018128</v>
+        <v>0.1063957984</v>
       </c>
       <c r="P15">
-        <v>0.5617595172000002</v>
+        <v>0.5585779416000002</v>
       </c>
       <c r="Q15">
-        <v>0.8587595172000002</v>
+        <v>0.8555779416000002</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1011231625642152</v>
+        <v>0.1016750066960402</v>
       </c>
       <c r="T15">
-        <v>0.7615441566104768</v>
+        <v>0.7691404988019288</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.58203481125709</v>
+        <v>13.5404608961673</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0933557857585946</v>
+        <v>0.09343066008632193</v>
       </c>
       <c r="C16">
-        <v>7.07652138607976</v>
+        <v>6.994476671746263</v>
       </c>
       <c r="D16">
-        <v>7.149721386079759</v>
+        <v>7.142976671746262</v>
       </c>
       <c r="E16">
-        <v>-2.8058</v>
+        <v>-2.730499999999999</v>
       </c>
       <c r="F16">
-        <v>1.0542</v>
+        <v>1.1295</v>
       </c>
       <c r="G16">
         <v>0.981</v>
@@ -2593,45 +2593,45 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M16">
-        <v>0.05302626</v>
+        <v>0.05850810000000001</v>
       </c>
       <c r="N16">
-        <v>0.6649737400000002</v>
+        <v>0.6594919000000001</v>
       </c>
       <c r="O16">
-        <v>0.1063957984</v>
+        <v>0.105518704</v>
       </c>
       <c r="P16">
-        <v>0.5585779416000002</v>
+        <v>0.5539731960000001</v>
       </c>
       <c r="Q16">
-        <v>0.8555779416000002</v>
+        <v>0.850973196</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1016750066960402</v>
+        <v>0.1022398353956729</v>
       </c>
       <c r="T16">
-        <v>0.7691404988019288</v>
+        <v>0.7769155784567089</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.16</v>
       </c>
       <c r="W16">
-        <v>0.042252</v>
+        <v>0.043512</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.5404608961673</v>
+        <v>12.27180510049036</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09343066008632193</v>
+        <v>0.09332913441404928</v>
       </c>
       <c r="C17">
-        <v>6.994476671746263</v>
+        <v>6.928325226459491</v>
       </c>
       <c r="D17">
-        <v>7.142976671746262</v>
+        <v>7.152125226459491</v>
       </c>
       <c r="E17">
-        <v>-2.730499999999999</v>
+        <v>-2.6552</v>
       </c>
       <c r="F17">
-        <v>1.1295</v>
+        <v>1.2048</v>
       </c>
       <c r="G17">
         <v>0.981</v>
@@ -2675,28 +2675,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M17">
-        <v>0.05850809999999999</v>
+        <v>0.06240863999999999</v>
       </c>
       <c r="N17">
-        <v>0.6594919000000002</v>
+        <v>0.6555913600000002</v>
       </c>
       <c r="O17">
-        <v>0.105518704</v>
+        <v>0.1048946176</v>
       </c>
       <c r="P17">
-        <v>0.5539731960000002</v>
+        <v>0.5506967424000001</v>
       </c>
       <c r="Q17">
-        <v>0.8509731960000002</v>
+        <v>0.8476967424000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1022398353956729</v>
+        <v>0.1028181123976777</v>
       </c>
       <c r="T17">
-        <v>0.7769155784567089</v>
+        <v>0.7848757790556505</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.27180510049036</v>
+        <v>11.50481728170972</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09332913441404928</v>
+        <v>0.09322760874177662</v>
       </c>
       <c r="C18">
-        <v>6.928325226459491</v>
+        <v>6.862197245728347</v>
       </c>
       <c r="D18">
-        <v>7.152125226459491</v>
+        <v>7.161297245728346</v>
       </c>
       <c r="E18">
-        <v>-2.6552</v>
+        <v>-2.579899999999999</v>
       </c>
       <c r="F18">
-        <v>1.2048</v>
+        <v>1.2801</v>
       </c>
       <c r="G18">
         <v>0.981</v>
@@ -2757,28 +2757,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M18">
-        <v>0.06240863999999999</v>
+        <v>0.06630918</v>
       </c>
       <c r="N18">
-        <v>0.6555913600000002</v>
+        <v>0.6516908200000002</v>
       </c>
       <c r="O18">
-        <v>0.1048946176</v>
+        <v>0.1042705312</v>
       </c>
       <c r="P18">
-        <v>0.5506967424000001</v>
+        <v>0.5474202888000002</v>
       </c>
       <c r="Q18">
-        <v>0.8476967424000001</v>
+        <v>0.8444202888000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1028181123976777</v>
+        <v>0.103410323785273</v>
       </c>
       <c r="T18">
-        <v>0.7848757790556505</v>
+        <v>0.7930277917172175</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.50481728170972</v>
+        <v>10.82806332396209</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09322760874177662</v>
+        <v>0.09312608306950397</v>
       </c>
       <c r="C19">
-        <v>6.862197245728347</v>
+        <v>6.796092819942903</v>
       </c>
       <c r="D19">
-        <v>7.161297245728346</v>
+        <v>7.170492819942901</v>
       </c>
       <c r="E19">
-        <v>-2.579899999999999</v>
+        <v>-2.504599999999999</v>
       </c>
       <c r="F19">
-        <v>1.2801</v>
+        <v>1.3554</v>
       </c>
       <c r="G19">
         <v>0.981</v>
@@ -2839,28 +2839,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M19">
-        <v>0.06630918</v>
+        <v>0.07020971999999999</v>
       </c>
       <c r="N19">
-        <v>0.6516908200000002</v>
+        <v>0.6477902800000002</v>
       </c>
       <c r="O19">
-        <v>0.1042705312</v>
+        <v>0.1036464448</v>
       </c>
       <c r="P19">
-        <v>0.5474202888000002</v>
+        <v>0.5441438352000001</v>
       </c>
       <c r="Q19">
-        <v>0.8444202888000001</v>
+        <v>0.8411438352</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.103410323785273</v>
+        <v>0.1040169793530536</v>
       </c>
       <c r="T19">
-        <v>0.7930277917172175</v>
+        <v>0.8013786339558956</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.82806332396209</v>
+        <v>10.22650425040864</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09312608306950398</v>
+        <v>0.0932958773972313</v>
       </c>
       <c r="C20">
-        <v>6.796092819942901</v>
+        <v>6.7054271389592</v>
       </c>
       <c r="D20">
-        <v>7.1704928199429</v>
+        <v>7.1551271389592</v>
       </c>
       <c r="E20">
-        <v>-2.504599999999999</v>
+        <v>-2.4293</v>
       </c>
       <c r="F20">
-        <v>1.3554</v>
+        <v>1.4307</v>
       </c>
       <c r="G20">
         <v>0.981</v>
@@ -2921,45 +2921,45 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M20">
-        <v>0.07020971999999999</v>
+        <v>0.07654244999999998</v>
       </c>
       <c r="N20">
-        <v>0.6477902800000002</v>
+        <v>0.6414575500000002</v>
       </c>
       <c r="O20">
-        <v>0.1036464448</v>
+        <v>0.102633208</v>
       </c>
       <c r="P20">
-        <v>0.5441438352000001</v>
+        <v>0.5388243420000001</v>
       </c>
       <c r="Q20">
-        <v>0.8411438352</v>
+        <v>0.835824342</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1040169793530536</v>
+        <v>0.1046386140706559</v>
       </c>
       <c r="T20">
-        <v>0.8013786339558956</v>
+        <v>0.8099356698300966</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.16</v>
       </c>
       <c r="W20">
-        <v>0.043512</v>
+        <v>0.04494</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.22650425040864</v>
+        <v>9.38041570396558</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0932958773972313</v>
+        <v>0.09320863172495863</v>
       </c>
       <c r="C21">
-        <v>6.7054271389592</v>
+        <v>6.638014275137268</v>
       </c>
       <c r="D21">
-        <v>7.1551271389592</v>
+        <v>7.163014275137267</v>
       </c>
       <c r="E21">
-        <v>-2.4293</v>
+        <v>-2.353999999999999</v>
       </c>
       <c r="F21">
-        <v>1.4307</v>
+        <v>1.506</v>
       </c>
       <c r="G21">
         <v>0.981</v>
@@ -3003,28 +3003,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M21">
-        <v>0.07654244999999998</v>
+        <v>0.080571</v>
       </c>
       <c r="N21">
-        <v>0.6414575500000002</v>
+        <v>0.6374290000000002</v>
       </c>
       <c r="O21">
-        <v>0.102633208</v>
+        <v>0.10198864</v>
       </c>
       <c r="P21">
-        <v>0.5388243420000001</v>
+        <v>0.5354403600000002</v>
       </c>
       <c r="Q21">
-        <v>0.835824342</v>
+        <v>0.8324403600000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1046386140706559</v>
+        <v>0.1052757896561983</v>
       </c>
       <c r="T21">
-        <v>0.8099356698300966</v>
+        <v>0.8187066316011528</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.38041570396558</v>
+        <v>8.9113949187673</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09320863172495863</v>
+        <v>0.09312138605268599</v>
       </c>
       <c r="C22">
-        <v>6.638014275137268</v>
+        <v>6.570618818571019</v>
       </c>
       <c r="D22">
-        <v>7.163014275137267</v>
+        <v>7.170918818571018</v>
       </c>
       <c r="E22">
-        <v>-2.353999999999999</v>
+        <v>-2.2787</v>
       </c>
       <c r="F22">
-        <v>1.506</v>
+        <v>1.5813</v>
       </c>
       <c r="G22">
         <v>0.981</v>
@@ -3085,28 +3085,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M22">
-        <v>0.080571</v>
+        <v>0.08459955</v>
       </c>
       <c r="N22">
-        <v>0.6374290000000002</v>
+        <v>0.6334004500000002</v>
       </c>
       <c r="O22">
-        <v>0.10198864</v>
+        <v>0.101344072</v>
       </c>
       <c r="P22">
-        <v>0.5354403600000002</v>
+        <v>0.5320563780000002</v>
       </c>
       <c r="Q22">
-        <v>0.8324403600000001</v>
+        <v>0.8290563780000002</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1052757896561983</v>
+        <v>0.1059290962692228</v>
       </c>
       <c r="T22">
-        <v>0.8187066316011528</v>
+        <v>0.827699643037299</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.9113949187673</v>
+        <v>8.487042779778381</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09312138605268599</v>
+        <v>0.09303414038041334</v>
       </c>
       <c r="C23">
-        <v>6.570618818571019</v>
+        <v>6.503240826951989</v>
       </c>
       <c r="D23">
-        <v>7.170918818571018</v>
+        <v>7.178840826951988</v>
       </c>
       <c r="E23">
-        <v>-2.2787</v>
+        <v>-2.203399999999999</v>
       </c>
       <c r="F23">
-        <v>1.5813</v>
+        <v>1.6566</v>
       </c>
       <c r="G23">
         <v>0.981</v>
@@ -3167,28 +3167,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M23">
-        <v>0.08459954999999998</v>
+        <v>0.08862809999999999</v>
       </c>
       <c r="N23">
-        <v>0.6334004500000002</v>
+        <v>0.6293719000000002</v>
       </c>
       <c r="O23">
-        <v>0.101344072</v>
+        <v>0.100699504</v>
       </c>
       <c r="P23">
-        <v>0.5320563780000002</v>
+        <v>0.5286723960000002</v>
       </c>
       <c r="Q23">
-        <v>0.8290563780000002</v>
+        <v>0.8256723960000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1059290962692228</v>
+        <v>0.1065991543338632</v>
       </c>
       <c r="T23">
-        <v>0.827699643037299</v>
+        <v>0.8369232445102693</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.487042779778385</v>
+        <v>8.101268107970274</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09303414038041334</v>
+        <v>0.09294689470814067</v>
       </c>
       <c r="C24">
-        <v>6.503240826951989</v>
+        <v>6.435880358226925</v>
       </c>
       <c r="D24">
-        <v>7.178840826951988</v>
+        <v>7.186780358226923</v>
       </c>
       <c r="E24">
-        <v>-2.203399999999999</v>
+        <v>-2.128099999999999</v>
       </c>
       <c r="F24">
-        <v>1.6566</v>
+        <v>1.7319</v>
       </c>
       <c r="G24">
         <v>0.981</v>
@@ -3249,28 +3249,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M24">
-        <v>0.08862809999999999</v>
+        <v>0.09265664999999999</v>
       </c>
       <c r="N24">
-        <v>0.6293719000000002</v>
+        <v>0.6253433500000002</v>
       </c>
       <c r="O24">
-        <v>0.100699504</v>
+        <v>0.100054936</v>
       </c>
       <c r="P24">
-        <v>0.5286723960000002</v>
+        <v>0.5252884140000001</v>
       </c>
       <c r="Q24">
-        <v>0.8256723960000001</v>
+        <v>0.8222884140000002</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1065991543338632</v>
+        <v>0.1072866165040788</v>
       </c>
       <c r="T24">
-        <v>0.8369232445102693</v>
+        <v>0.8463864200474728</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.101268107970274</v>
+        <v>7.749039059797654</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09294689470814067</v>
+        <v>0.09302092903586802</v>
       </c>
       <c r="C25">
-        <v>6.435880358226925</v>
+        <v>6.353841958569825</v>
       </c>
       <c r="D25">
-        <v>7.186780358226923</v>
+        <v>7.180041958569825</v>
       </c>
       <c r="E25">
-        <v>-2.128099999999999</v>
+        <v>-2.0528</v>
       </c>
       <c r="F25">
-        <v>1.7319</v>
+        <v>1.8072</v>
       </c>
       <c r="G25">
         <v>0.981</v>
@@ -3331,45 +3331,45 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M25">
-        <v>0.09265664999999999</v>
+        <v>0.09813096</v>
       </c>
       <c r="N25">
-        <v>0.6253433500000002</v>
+        <v>0.6198690400000002</v>
       </c>
       <c r="O25">
-        <v>0.100054936</v>
+        <v>0.09917904640000004</v>
       </c>
       <c r="P25">
-        <v>0.5252884140000001</v>
+        <v>0.5206899936000001</v>
       </c>
       <c r="Q25">
-        <v>0.8222884140000002</v>
+        <v>0.8176899936000002</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1072866165040788</v>
+        <v>0.1079921697840369</v>
       </c>
       <c r="T25">
-        <v>0.8463864200474728</v>
+        <v>0.8560986265198658</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.16</v>
       </c>
       <c r="W25">
-        <v>0.04494</v>
+        <v>0.045612</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.749039059797654</v>
+        <v>7.316753041038223</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09302092903586801</v>
+        <v>0.09294040336359534</v>
       </c>
       <c r="C26">
-        <v>6.353841958569825</v>
+        <v>6.285871785595505</v>
       </c>
       <c r="D26">
-        <v>7.180041958569825</v>
+        <v>7.187371785595505</v>
       </c>
       <c r="E26">
-        <v>-2.0528</v>
+        <v>-1.9775</v>
       </c>
       <c r="F26">
-        <v>1.8072</v>
+        <v>1.8825</v>
       </c>
       <c r="G26">
         <v>0.981</v>
@@ -3413,28 +3413,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M26">
-        <v>0.09813095999999999</v>
+        <v>0.10221975</v>
       </c>
       <c r="N26">
-        <v>0.6198690400000002</v>
+        <v>0.6157802500000003</v>
       </c>
       <c r="O26">
-        <v>0.09917904640000004</v>
+        <v>0.09852484000000004</v>
       </c>
       <c r="P26">
-        <v>0.5206899936000001</v>
+        <v>0.5172554100000002</v>
       </c>
       <c r="Q26">
-        <v>0.8176899936000002</v>
+        <v>0.8142554100000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1079921697840369</v>
+        <v>0.1087165378181271</v>
       </c>
       <c r="T26">
-        <v>0.8560986265198658</v>
+        <v>0.8660698251648559</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.316753041038224</v>
+        <v>7.024082919396695</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09294040336359534</v>
+        <v>0.09285987769132269</v>
       </c>
       <c r="C27">
-        <v>6.285871785595505</v>
+        <v>6.217916593388078</v>
       </c>
       <c r="D27">
-        <v>7.187371785595505</v>
+        <v>7.194716593388078</v>
       </c>
       <c r="E27">
-        <v>-1.9775</v>
+        <v>-1.902199999999999</v>
       </c>
       <c r="F27">
-        <v>1.8825</v>
+        <v>1.9578</v>
       </c>
       <c r="G27">
         <v>0.981</v>
@@ -3495,28 +3495,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M27">
-        <v>0.10221975</v>
+        <v>0.10630854</v>
       </c>
       <c r="N27">
-        <v>0.6157802500000003</v>
+        <v>0.6116914600000002</v>
       </c>
       <c r="O27">
-        <v>0.09852484000000004</v>
+        <v>0.09787063360000003</v>
       </c>
       <c r="P27">
-        <v>0.5172554100000002</v>
+        <v>0.5138208264000002</v>
       </c>
       <c r="Q27">
-        <v>0.8142554100000001</v>
+        <v>0.8108208264000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1087165378181271</v>
+        <v>0.1094604833666523</v>
       </c>
       <c r="T27">
-        <v>0.8660698251648559</v>
+        <v>0.8763105156651161</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.024082919396695</v>
+        <v>6.753925884035282</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09285987769132269</v>
+        <v>0.09277935201905005</v>
       </c>
       <c r="C28">
-        <v>6.217916593388078</v>
+        <v>6.149976427921266</v>
       </c>
       <c r="D28">
-        <v>7.194716593388078</v>
+        <v>7.202076427921266</v>
       </c>
       <c r="E28">
-        <v>-1.902199999999999</v>
+        <v>-1.826899999999999</v>
       </c>
       <c r="F28">
-        <v>1.9578</v>
+        <v>2.0331</v>
       </c>
       <c r="G28">
         <v>0.981</v>
@@ -3577,28 +3577,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M28">
-        <v>0.10630854</v>
+        <v>0.11039733</v>
       </c>
       <c r="N28">
-        <v>0.6116914600000002</v>
+        <v>0.6076026700000001</v>
       </c>
       <c r="O28">
-        <v>0.09787063360000003</v>
+        <v>0.09721642720000002</v>
       </c>
       <c r="P28">
-        <v>0.5138208264000002</v>
+        <v>0.5103862428000001</v>
       </c>
       <c r="Q28">
-        <v>0.8108208264000001</v>
+        <v>0.8073862428</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1094604833666523</v>
+        <v>0.1102248109850001</v>
       </c>
       <c r="T28">
-        <v>0.8763105156651161</v>
+        <v>0.886831773028397</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.753925884035282</v>
+        <v>6.503780480922863</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09277935201905005</v>
+        <v>0.09269882634677737</v>
       </c>
       <c r="C29">
-        <v>6.149976427921266</v>
+        <v>6.082051335357107</v>
       </c>
       <c r="D29">
-        <v>7.202076427921266</v>
+        <v>7.209451335357106</v>
       </c>
       <c r="E29">
-        <v>-1.826899999999999</v>
+        <v>-1.751599999999999</v>
       </c>
       <c r="F29">
-        <v>2.0331</v>
+        <v>2.1084</v>
       </c>
       <c r="G29">
         <v>0.981</v>
@@ -3659,28 +3659,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M29">
-        <v>0.11039733</v>
+        <v>0.11448612</v>
       </c>
       <c r="N29">
-        <v>0.6076026700000001</v>
+        <v>0.6035138800000002</v>
       </c>
       <c r="O29">
-        <v>0.09721642720000002</v>
+        <v>0.09656222080000003</v>
       </c>
       <c r="P29">
-        <v>0.5103862428000001</v>
+        <v>0.5069516592000002</v>
       </c>
       <c r="Q29">
-        <v>0.8073862428</v>
+        <v>0.8039516592000002</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1102248109850001</v>
+        <v>0.1110103699260797</v>
       </c>
       <c r="T29">
-        <v>0.886831773028397</v>
+        <v>0.8976452875406579</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.503780480922863</v>
+        <v>6.27150260660419</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09269882634677737</v>
+        <v>0.09286190067450471</v>
       </c>
       <c r="C30">
-        <v>6.082051335357107</v>
+        <v>5.991831891736091</v>
       </c>
       <c r="D30">
-        <v>7.209451335357106</v>
+        <v>7.194531891736091</v>
       </c>
       <c r="E30">
-        <v>-1.751599999999999</v>
+        <v>-1.676299999999999</v>
       </c>
       <c r="F30">
-        <v>2.1084</v>
+        <v>2.1837</v>
       </c>
       <c r="G30">
         <v>0.981</v>
@@ -3741,45 +3741,45 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M30">
-        <v>0.11448612</v>
+        <v>0.12075861</v>
       </c>
       <c r="N30">
-        <v>0.6035138800000002</v>
+        <v>0.5972413900000002</v>
       </c>
       <c r="O30">
-        <v>0.09656222080000003</v>
+        <v>0.09555862240000003</v>
       </c>
       <c r="P30">
-        <v>0.5069516592000002</v>
+        <v>0.5016827676000002</v>
       </c>
       <c r="Q30">
-        <v>0.8039516592000002</v>
+        <v>0.7986827676000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1110103699260797</v>
+        <v>0.1118180572880348</v>
       </c>
       <c r="T30">
-        <v>0.8976452875406579</v>
+        <v>0.9087634080955178</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.16</v>
       </c>
       <c r="W30">
-        <v>0.045612</v>
+        <v>0.046452</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.27150260660419</v>
+        <v>5.945745814729071</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09286190067450471</v>
+        <v>0.09278977500223204</v>
       </c>
       <c r="C31">
-        <v>5.991831891736091</v>
+        <v>5.923122946439587</v>
       </c>
       <c r="D31">
-        <v>7.194531891736091</v>
+        <v>7.201122946439588</v>
       </c>
       <c r="E31">
-        <v>-1.6763</v>
+        <v>-1.601</v>
       </c>
       <c r="F31">
-        <v>2.1837</v>
+        <v>2.259</v>
       </c>
       <c r="G31">
         <v>0.981</v>
@@ -3823,28 +3823,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M31">
-        <v>0.12075861</v>
+        <v>0.1249227</v>
       </c>
       <c r="N31">
-        <v>0.5972413900000002</v>
+        <v>0.5930773000000003</v>
       </c>
       <c r="O31">
-        <v>0.09555862240000003</v>
+        <v>0.09489236800000005</v>
       </c>
       <c r="P31">
-        <v>0.5016827676000002</v>
+        <v>0.4981849320000002</v>
       </c>
       <c r="Q31">
-        <v>0.7986827676000001</v>
+        <v>0.7951849320000002</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1118180572880348</v>
+        <v>0.1126488214317601</v>
       </c>
       <c r="T31">
-        <v>0.9087634080955177</v>
+        <v>0.9201991892376593</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.945745814729072</v>
+        <v>5.747554287571436</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09278977500223204</v>
+        <v>0.09271764932995939</v>
       </c>
       <c r="C32">
-        <v>5.923122946439587</v>
+        <v>5.854426088610992</v>
       </c>
       <c r="D32">
-        <v>7.201122946439588</v>
+        <v>7.207726088610991</v>
       </c>
       <c r="E32">
-        <v>-1.601</v>
+        <v>-1.5257</v>
       </c>
       <c r="F32">
-        <v>2.259</v>
+        <v>2.3343</v>
       </c>
       <c r="G32">
         <v>0.981</v>
@@ -3905,28 +3905,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M32">
-        <v>0.1249227</v>
+        <v>0.12908679</v>
       </c>
       <c r="N32">
-        <v>0.5930773000000003</v>
+        <v>0.5889132100000002</v>
       </c>
       <c r="O32">
-        <v>0.09489236800000005</v>
+        <v>0.09422611360000004</v>
       </c>
       <c r="P32">
-        <v>0.4981849320000002</v>
+        <v>0.4946870964000001</v>
       </c>
       <c r="Q32">
-        <v>0.7951849320000002</v>
+        <v>0.7916870964000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1126488214317601</v>
+        <v>0.1135036656955933</v>
       </c>
       <c r="T32">
-        <v>0.9201991892376593</v>
+        <v>0.9319664422969645</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.747554287571436</v>
+        <v>5.562149310553002</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09271764932995939</v>
+        <v>0.09264552365768673</v>
       </c>
       <c r="C33">
-        <v>5.854426088610992</v>
+        <v>5.785741351532002</v>
       </c>
       <c r="D33">
-        <v>7.207726088610991</v>
+        <v>7.214341351532</v>
       </c>
       <c r="E33">
-        <v>-1.5257</v>
+        <v>-1.4504</v>
       </c>
       <c r="F33">
-        <v>2.3343</v>
+        <v>2.4096</v>
       </c>
       <c r="G33">
         <v>0.981</v>
@@ -3987,28 +3987,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M33">
-        <v>0.12908679</v>
+        <v>0.13325088</v>
       </c>
       <c r="N33">
-        <v>0.5889132100000002</v>
+        <v>0.5847491200000002</v>
       </c>
       <c r="O33">
-        <v>0.09422611360000004</v>
+        <v>0.09355985920000004</v>
       </c>
       <c r="P33">
-        <v>0.4946870964000001</v>
+        <v>0.4911892608000002</v>
       </c>
       <c r="Q33">
-        <v>0.7916870964000001</v>
+        <v>0.7881892608000002</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1135036656955933</v>
+        <v>0.1143836524377746</v>
       </c>
       <c r="T33">
-        <v>0.9319664422969645</v>
+        <v>0.9440797910344844</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.562149310553002</v>
+        <v>5.388332144598222</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09264552365768673</v>
+        <v>0.09257339798541409</v>
       </c>
       <c r="C34">
-        <v>5.785741351532002</v>
+        <v>5.717068768606605</v>
       </c>
       <c r="D34">
-        <v>7.214341351532</v>
+        <v>7.220968768606604</v>
       </c>
       <c r="E34">
-        <v>-1.4504</v>
+        <v>-1.375099999999999</v>
       </c>
       <c r="F34">
-        <v>2.4096</v>
+        <v>2.4849</v>
       </c>
       <c r="G34">
         <v>0.981</v>
@@ -4069,28 +4069,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M34">
-        <v>0.13325088</v>
+        <v>0.13741497</v>
       </c>
       <c r="N34">
-        <v>0.5847491200000002</v>
+        <v>0.5805850300000002</v>
       </c>
       <c r="O34">
-        <v>0.09355985920000004</v>
+        <v>0.09289360480000003</v>
       </c>
       <c r="P34">
-        <v>0.4911892608000002</v>
+        <v>0.4876914252000001</v>
       </c>
       <c r="Q34">
-        <v>0.7881892608000002</v>
+        <v>0.7846914252000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1143836524377746</v>
+        <v>0.1152899074409166</v>
       </c>
       <c r="T34">
-        <v>0.9440797910344844</v>
+        <v>0.9565547322716319</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.388332144598222</v>
+        <v>5.225049352337669</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09257339798541409</v>
+        <v>0.09250127231314141</v>
       </c>
       <c r="C35">
-        <v>5.717068768606605</v>
+        <v>5.648408373361654</v>
       </c>
       <c r="D35">
-        <v>7.220968768606604</v>
+        <v>7.227608373361654</v>
       </c>
       <c r="E35">
-        <v>-1.375099999999999</v>
+        <v>-1.299799999999999</v>
       </c>
       <c r="F35">
-        <v>2.4849</v>
+        <v>2.5602</v>
       </c>
       <c r="G35">
         <v>0.981</v>
@@ -4151,28 +4151,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M35">
-        <v>0.13741497</v>
+        <v>0.14157906</v>
       </c>
       <c r="N35">
-        <v>0.5805850300000002</v>
+        <v>0.5764209400000002</v>
       </c>
       <c r="O35">
-        <v>0.09289360480000003</v>
+        <v>0.09222735040000003</v>
       </c>
       <c r="P35">
-        <v>0.4876914252000001</v>
+        <v>0.4841935896000002</v>
       </c>
       <c r="Q35">
-        <v>0.7846914252000001</v>
+        <v>0.7811935896000002</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1152899074409166</v>
+        <v>0.1162236247168809</v>
       </c>
       <c r="T35">
-        <v>0.9565547322716319</v>
+        <v>0.9694077020311171</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.225049352337669</v>
+        <v>5.071371430210091</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09250127231314141</v>
+        <v>0.09242914664086876</v>
       </c>
       <c r="C36">
-        <v>5.648408373361654</v>
+        <v>5.579760199447415</v>
       </c>
       <c r="D36">
-        <v>7.227608373361654</v>
+        <v>7.234260199447416</v>
       </c>
       <c r="E36">
-        <v>-1.299799999999999</v>
+        <v>-1.224499999999999</v>
       </c>
       <c r="F36">
-        <v>2.5602</v>
+        <v>2.6355</v>
       </c>
       <c r="G36">
         <v>0.981</v>
@@ -4233,28 +4233,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M36">
-        <v>0.14157906</v>
+        <v>0.14574315</v>
       </c>
       <c r="N36">
-        <v>0.5764209400000002</v>
+        <v>0.5722568500000002</v>
       </c>
       <c r="O36">
-        <v>0.09222735040000003</v>
+        <v>0.09156109600000002</v>
       </c>
       <c r="P36">
-        <v>0.4841935896000002</v>
+        <v>0.4806957540000001</v>
       </c>
       <c r="Q36">
-        <v>0.7811935896000002</v>
+        <v>0.7776957540000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1162236247168809</v>
+        <v>0.1171860717551827</v>
       </c>
       <c r="T36">
-        <v>0.9694077020311171</v>
+        <v>0.9826561477832019</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.071371430210091</v>
+        <v>4.926475103632658</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09242914664086876</v>
+        <v>0.0923570209685961</v>
       </c>
       <c r="C37">
-        <v>5.579760199447415</v>
+        <v>5.511124280638161</v>
       </c>
       <c r="D37">
-        <v>7.234260199447416</v>
+        <v>7.240924280638161</v>
       </c>
       <c r="E37">
-        <v>-1.224499999999999</v>
+        <v>-1.1492</v>
       </c>
       <c r="F37">
-        <v>2.6355</v>
+        <v>2.7108</v>
       </c>
       <c r="G37">
         <v>0.981</v>
@@ -4315,28 +4315,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M37">
-        <v>0.14574315</v>
+        <v>0.14990724</v>
       </c>
       <c r="N37">
-        <v>0.5722568500000002</v>
+        <v>0.5680927600000002</v>
       </c>
       <c r="O37">
-        <v>0.09156109600000002</v>
+        <v>0.09089484160000004</v>
       </c>
       <c r="P37">
-        <v>0.4806957540000001</v>
+        <v>0.4771979184000001</v>
       </c>
       <c r="Q37">
-        <v>0.7776957540000001</v>
+        <v>0.7741979184000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1171860717551827</v>
+        <v>0.1181785952634314</v>
       </c>
       <c r="T37">
-        <v>0.9826561477832019</v>
+        <v>0.9963186074650394</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.926475103632658</v>
+        <v>4.789628572976197</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0923570209685961</v>
+        <v>0.09228489529632347</v>
       </c>
       <c r="C38">
-        <v>5.511124280638161</v>
+        <v>5.442500650832713</v>
       </c>
       <c r="D38">
-        <v>7.240924280638161</v>
+        <v>7.247600650832712</v>
       </c>
       <c r="E38">
-        <v>-1.1492</v>
+        <v>-1.0739</v>
       </c>
       <c r="F38">
-        <v>2.7108</v>
+        <v>2.7861</v>
       </c>
       <c r="G38">
         <v>0.981</v>
@@ -4397,28 +4397,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M38">
-        <v>0.14990724</v>
+        <v>0.15407133</v>
       </c>
       <c r="N38">
-        <v>0.5680927600000002</v>
+        <v>0.5639286700000001</v>
       </c>
       <c r="O38">
-        <v>0.09089484160000004</v>
+        <v>0.09022858720000003</v>
       </c>
       <c r="P38">
-        <v>0.4771979184000001</v>
+        <v>0.4737000828000001</v>
       </c>
       <c r="Q38">
-        <v>0.7741979184000001</v>
+        <v>0.7707000828000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1181785952634314</v>
+        <v>0.1192026274544817</v>
       </c>
       <c r="T38">
-        <v>0.9963186074650392</v>
+        <v>1.010414796025665</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.789628572976197</v>
+        <v>4.660179152084947</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09228489529632347</v>
+        <v>0.09221276962405078</v>
       </c>
       <c r="C39">
-        <v>5.442500650832713</v>
+        <v>5.373889344055048</v>
       </c>
       <c r="D39">
-        <v>7.247600650832712</v>
+        <v>7.254289344055048</v>
       </c>
       <c r="E39">
-        <v>-1.0739</v>
+        <v>-0.9985999999999997</v>
       </c>
       <c r="F39">
-        <v>2.7861</v>
+        <v>2.8614</v>
       </c>
       <c r="G39">
         <v>0.981</v>
@@ -4479,28 +4479,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M39">
-        <v>0.15407133</v>
+        <v>0.15823542</v>
       </c>
       <c r="N39">
-        <v>0.5639286700000001</v>
+        <v>0.5597645800000002</v>
       </c>
       <c r="O39">
-        <v>0.09022858720000003</v>
+        <v>0.08956233280000003</v>
       </c>
       <c r="P39">
-        <v>0.4737000828000001</v>
+        <v>0.4702022472000001</v>
       </c>
       <c r="Q39">
-        <v>0.7707000828000001</v>
+        <v>0.7672022472000002</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1192026274544817</v>
+        <v>0.1202596929420174</v>
       </c>
       <c r="T39">
-        <v>1.010414796025665</v>
+        <v>1.024965700346311</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.660179152084947</v>
+        <v>4.537542858609029</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09221276962405078</v>
+        <v>0.09295964395177812</v>
       </c>
       <c r="C40">
-        <v>5.373889344055048</v>
+        <v>5.229919056006782</v>
       </c>
       <c r="D40">
-        <v>7.254289344055048</v>
+        <v>7.185619056006782</v>
       </c>
       <c r="E40">
-        <v>-0.9985999999999997</v>
+        <v>-0.9232999999999998</v>
       </c>
       <c r="F40">
-        <v>2.8614</v>
+        <v>2.9367</v>
       </c>
       <c r="G40">
         <v>0.981</v>
@@ -4561,45 +4561,45 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M40">
-        <v>0.15823542</v>
+        <v>0.16974126</v>
       </c>
       <c r="N40">
-        <v>0.5597645800000002</v>
+        <v>0.5482587400000002</v>
       </c>
       <c r="O40">
-        <v>0.08956233280000003</v>
+        <v>0.08772139840000003</v>
       </c>
       <c r="P40">
-        <v>0.4702022472000001</v>
+        <v>0.4605373416000001</v>
       </c>
       <c r="Q40">
-        <v>0.7672022472000002</v>
+        <v>0.7575373416000002</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1202596929420174</v>
+        <v>0.1213514163143904</v>
       </c>
       <c r="T40">
-        <v>1.024965700346311</v>
+        <v>1.039993683497142</v>
       </c>
       <c r="U40">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.16</v>
       </c>
       <c r="W40">
-        <v>0.046452</v>
+        <v>0.048552</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.537542858609029</v>
+        <v>4.229967422181266</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09295964395177812</v>
+        <v>0.09290851827950547</v>
       </c>
       <c r="C41">
-        <v>5.229919056006782</v>
+        <v>5.159278254283604</v>
       </c>
       <c r="D41">
-        <v>7.185619056006782</v>
+        <v>7.190278254283604</v>
       </c>
       <c r="E41">
-        <v>-0.9232999999999998</v>
+        <v>-0.8479999999999994</v>
       </c>
       <c r="F41">
-        <v>2.9367</v>
+        <v>3.012</v>
       </c>
       <c r="G41">
         <v>0.981</v>
@@ -4643,28 +4643,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M41">
-        <v>0.16974126</v>
+        <v>0.1740936</v>
       </c>
       <c r="N41">
-        <v>0.5482587400000002</v>
+        <v>0.5439064000000002</v>
       </c>
       <c r="O41">
-        <v>0.08772139840000003</v>
+        <v>0.08702502400000003</v>
       </c>
       <c r="P41">
-        <v>0.4605373416000001</v>
+        <v>0.4568813760000002</v>
       </c>
       <c r="Q41">
-        <v>0.7575373416000002</v>
+        <v>0.7538813760000003</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1213514163143904</v>
+        <v>0.1224795304658425</v>
       </c>
       <c r="T41">
-        <v>1.039993683497142</v>
+        <v>1.055522599419668</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.229967422181266</v>
+        <v>4.124218236626735</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09290851827950547</v>
+        <v>0.0928573926072328</v>
       </c>
       <c r="C42">
-        <v>5.159278254283604</v>
+        <v>5.088643498584639</v>
       </c>
       <c r="D42">
-        <v>7.190278254283604</v>
+        <v>7.194943498584638</v>
       </c>
       <c r="E42">
-        <v>-0.8479999999999994</v>
+        <v>-0.7726999999999995</v>
       </c>
       <c r="F42">
-        <v>3.012</v>
+        <v>3.0873</v>
       </c>
       <c r="G42">
         <v>0.981</v>
@@ -4725,28 +4725,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M42">
-        <v>0.1740936</v>
+        <v>0.17844594</v>
       </c>
       <c r="N42">
-        <v>0.5439064000000002</v>
+        <v>0.5395540600000002</v>
       </c>
       <c r="O42">
-        <v>0.08702502400000003</v>
+        <v>0.08632864960000003</v>
       </c>
       <c r="P42">
-        <v>0.4568813760000002</v>
+        <v>0.4532254104000001</v>
       </c>
       <c r="Q42">
-        <v>0.7538813760000003</v>
+        <v>0.7502254104000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1224795304658425</v>
+        <v>0.1236458857749708</v>
       </c>
       <c r="T42">
-        <v>1.055522599419668</v>
+        <v>1.071577919271771</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.124218236626735</v>
+        <v>4.023627547928522</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0928573926072328</v>
+        <v>0.09404106693496013</v>
       </c>
       <c r="C43">
-        <v>5.088643498584639</v>
+        <v>4.906862060078364</v>
       </c>
       <c r="D43">
-        <v>7.194943498584638</v>
+        <v>7.088462060078363</v>
       </c>
       <c r="E43">
-        <v>-0.7726999999999995</v>
+        <v>-0.6973999999999996</v>
       </c>
       <c r="F43">
-        <v>3.0873</v>
+        <v>3.1626</v>
       </c>
       <c r="G43">
         <v>0.981</v>
@@ -4807,45 +4807,45 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M43">
-        <v>0.17844594</v>
+        <v>0.19386738</v>
       </c>
       <c r="N43">
-        <v>0.5395540600000002</v>
+        <v>0.5241326200000002</v>
       </c>
       <c r="O43">
-        <v>0.08632864960000003</v>
+        <v>0.08386121920000003</v>
       </c>
       <c r="P43">
-        <v>0.4532254104000001</v>
+        <v>0.4402714008000002</v>
       </c>
       <c r="Q43">
-        <v>0.7502254104000001</v>
+        <v>0.7372714008000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1236458857749708</v>
+        <v>0.1248524602326899</v>
       </c>
       <c r="T43">
-        <v>1.071577919271771</v>
+        <v>1.088186870842911</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0.16</v>
       </c>
       <c r="W43">
-        <v>0.048552</v>
+        <v>0.051492</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.023627547928522</v>
+        <v>3.703562713851088</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09404106693496014</v>
+        <v>0.09401934126268749</v>
       </c>
       <c r="C44">
-        <v>4.906862060078364</v>
+        <v>4.8334880655768</v>
       </c>
       <c r="D44">
-        <v>7.088462060078363</v>
+        <v>7.090388065576799</v>
       </c>
       <c r="E44">
-        <v>-0.6974</v>
+        <v>-0.6220999999999997</v>
       </c>
       <c r="F44">
-        <v>3.162599999999999</v>
+        <v>3.2379</v>
       </c>
       <c r="G44">
         <v>0.981</v>
@@ -4889,28 +4889,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M44">
-        <v>0.19386738</v>
+        <v>0.19848327</v>
       </c>
       <c r="N44">
-        <v>0.5241326200000003</v>
+        <v>0.5195167300000002</v>
       </c>
       <c r="O44">
-        <v>0.08386121920000005</v>
+        <v>0.08312267680000003</v>
       </c>
       <c r="P44">
-        <v>0.4402714008000002</v>
+        <v>0.4363940532000002</v>
       </c>
       <c r="Q44">
-        <v>0.7372714008000002</v>
+        <v>0.7333940532000002</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1248524602326899</v>
+        <v>0.1261013706362938</v>
       </c>
       <c r="T44">
-        <v>1.088186870842911</v>
+        <v>1.105378592644618</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.703562713851089</v>
+        <v>3.617433348412691</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09401934126268749</v>
+        <v>0.09399761559041483</v>
       </c>
       <c r="C45">
-        <v>4.8334880655768</v>
+        <v>4.760115117989315</v>
       </c>
       <c r="D45">
-        <v>7.090388065576799</v>
+        <v>7.092315117989314</v>
       </c>
       <c r="E45">
-        <v>-0.6220999999999997</v>
+        <v>-0.5467999999999997</v>
       </c>
       <c r="F45">
-        <v>3.2379</v>
+        <v>3.3132</v>
       </c>
       <c r="G45">
         <v>0.981</v>
@@ -4971,28 +4971,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M45">
-        <v>0.19848327</v>
+        <v>0.20309916</v>
       </c>
       <c r="N45">
-        <v>0.5195167300000002</v>
+        <v>0.5149008400000002</v>
       </c>
       <c r="O45">
-        <v>0.08312267680000003</v>
+        <v>0.08238413440000004</v>
       </c>
       <c r="P45">
-        <v>0.4363940532000002</v>
+        <v>0.4325167056000002</v>
       </c>
       <c r="Q45">
-        <v>0.7333940532000002</v>
+        <v>0.7295167056000003</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1261013706362938</v>
+        <v>0.1273948849828836</v>
       </c>
       <c r="T45">
-        <v>1.105378592644618</v>
+        <v>1.123184304510672</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.617433348412691</v>
+        <v>3.535218954130585</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09399761559041483</v>
+        <v>0.0950342899181422</v>
       </c>
       <c r="C46">
-        <v>4.760115117989315</v>
+        <v>4.594015360770613</v>
       </c>
       <c r="D46">
-        <v>7.092315117989314</v>
+        <v>7.001515360770613</v>
       </c>
       <c r="E46">
-        <v>-0.5467999999999997</v>
+        <v>-0.4714999999999998</v>
       </c>
       <c r="F46">
-        <v>3.3132</v>
+        <v>3.3885</v>
       </c>
       <c r="G46">
         <v>0.981</v>
@@ -5053,45 +5053,45 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M46">
-        <v>0.20309916</v>
+        <v>0.21720285</v>
       </c>
       <c r="N46">
-        <v>0.5149008400000002</v>
+        <v>0.5007971500000001</v>
       </c>
       <c r="O46">
-        <v>0.08238413440000004</v>
+        <v>0.08012754400000002</v>
       </c>
       <c r="P46">
-        <v>0.4325167056000002</v>
+        <v>0.4206696060000001</v>
       </c>
       <c r="Q46">
-        <v>0.7295167056000003</v>
+        <v>0.7176696060000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1273948849828836</v>
+        <v>0.128735436214804</v>
       </c>
       <c r="T46">
-        <v>1.123184304510672</v>
+        <v>1.141637496808219</v>
       </c>
       <c r="U46">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V46">
         <v>0.16</v>
       </c>
       <c r="W46">
-        <v>0.051492</v>
+        <v>0.053844</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.535218954130585</v>
+        <v>3.305665648494024</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0950342899181422</v>
+        <v>0.09503608424586951</v>
       </c>
       <c r="C47">
-        <v>4.594015360770613</v>
+        <v>4.518560215510916</v>
       </c>
       <c r="D47">
-        <v>7.001515360770613</v>
+        <v>7.001360215510916</v>
       </c>
       <c r="E47">
-        <v>-0.4714999999999998</v>
+        <v>-0.3961999999999994</v>
       </c>
       <c r="F47">
-        <v>3.3885</v>
+        <v>3.4638</v>
       </c>
       <c r="G47">
         <v>0.981</v>
@@ -5135,28 +5135,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M47">
-        <v>0.21720285</v>
+        <v>0.22202958</v>
       </c>
       <c r="N47">
-        <v>0.5007971500000001</v>
+        <v>0.4959704200000002</v>
       </c>
       <c r="O47">
-        <v>0.08012754400000002</v>
+        <v>0.07935526720000004</v>
       </c>
       <c r="P47">
-        <v>0.4206696060000001</v>
+        <v>0.4166151528000002</v>
       </c>
       <c r="Q47">
-        <v>0.7176696060000001</v>
+        <v>0.7136151528000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.128735436214804</v>
+        <v>0.130125637492351</v>
       </c>
       <c r="T47">
-        <v>1.141637496808219</v>
+        <v>1.160774140672342</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.305665648494024</v>
+        <v>3.233803351787632</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09503608424586951</v>
+        <v>0.09503787857359687</v>
       </c>
       <c r="C48">
-        <v>4.518560215510916</v>
+        <v>4.443105077126731</v>
       </c>
       <c r="D48">
-        <v>7.001360215510916</v>
+        <v>7.00120507712673</v>
       </c>
       <c r="E48">
-        <v>-0.3961999999999994</v>
+        <v>-0.3208999999999995</v>
       </c>
       <c r="F48">
-        <v>3.4638</v>
+        <v>3.5391</v>
       </c>
       <c r="G48">
         <v>0.981</v>
@@ -5217,28 +5217,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M48">
-        <v>0.22202958</v>
+        <v>0.22685631</v>
       </c>
       <c r="N48">
-        <v>0.4959704200000002</v>
+        <v>0.4911436900000002</v>
       </c>
       <c r="O48">
-        <v>0.07935526720000004</v>
+        <v>0.07858299040000004</v>
       </c>
       <c r="P48">
-        <v>0.4166151528000002</v>
+        <v>0.4125606996000001</v>
       </c>
       <c r="Q48">
-        <v>0.7136151528000001</v>
+        <v>0.7095606996000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.130125637492351</v>
+        <v>0.1315682991954658</v>
       </c>
       <c r="T48">
-        <v>1.160774140672342</v>
+        <v>1.180632922040771</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.233803351787632</v>
+        <v>3.164999025153853</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09503787857359687</v>
+        <v>0.0950396729013242</v>
       </c>
       <c r="C49">
-        <v>4.443105077126731</v>
+        <v>4.367649945617607</v>
       </c>
       <c r="D49">
-        <v>7.00120507712673</v>
+        <v>7.001049945617607</v>
       </c>
       <c r="E49">
-        <v>-0.3208999999999995</v>
+        <v>-0.2455999999999996</v>
       </c>
       <c r="F49">
-        <v>3.5391</v>
+        <v>3.6144</v>
       </c>
       <c r="G49">
         <v>0.981</v>
@@ -5299,28 +5299,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M49">
-        <v>0.22685631</v>
+        <v>0.23168304</v>
       </c>
       <c r="N49">
-        <v>0.4911436900000002</v>
+        <v>0.4863169600000002</v>
       </c>
       <c r="O49">
-        <v>0.07858299040000004</v>
+        <v>0.07781071360000003</v>
       </c>
       <c r="P49">
-        <v>0.4125606996000001</v>
+        <v>0.4085062464000002</v>
       </c>
       <c r="Q49">
-        <v>0.7095606996000001</v>
+        <v>0.7055062464000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1315682991954658</v>
+        <v>0.1330664478871619</v>
       </c>
       <c r="T49">
-        <v>1.180632922040771</v>
+        <v>1.201255502692601</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.164999025153853</v>
+        <v>3.099061545463147</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0950396729013242</v>
+        <v>0.09504146722905153</v>
       </c>
       <c r="C50">
-        <v>4.367649945617607</v>
+        <v>4.292194820983086</v>
       </c>
       <c r="D50">
-        <v>7.001049945617607</v>
+        <v>7.000894820983086</v>
       </c>
       <c r="E50">
-        <v>-0.2456</v>
+        <v>-0.1702999999999997</v>
       </c>
       <c r="F50">
-        <v>3.614399999999999</v>
+        <v>3.6897</v>
       </c>
       <c r="G50">
         <v>0.981</v>
@@ -5381,28 +5381,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M50">
-        <v>0.23168304</v>
+        <v>0.23650977</v>
       </c>
       <c r="N50">
-        <v>0.4863169600000002</v>
+        <v>0.4814902300000002</v>
       </c>
       <c r="O50">
-        <v>0.07781071360000004</v>
+        <v>0.07703843680000003</v>
       </c>
       <c r="P50">
-        <v>0.4085062464000002</v>
+        <v>0.4044517932000001</v>
       </c>
       <c r="Q50">
-        <v>0.7055062464000001</v>
+        <v>0.7014517932000002</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1330664478871619</v>
+        <v>0.1346233475079442</v>
       </c>
       <c r="T50">
-        <v>1.201255502692601</v>
+        <v>1.222686811997444</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.099061545463148</v>
+        <v>3.035815391474103</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09504146722905153</v>
+        <v>0.09831926155677888</v>
       </c>
       <c r="C51">
-        <v>4.292194820983086</v>
+        <v>3.944550066590705</v>
       </c>
       <c r="D51">
-        <v>7.000894820983086</v>
+        <v>6.728550066590705</v>
       </c>
       <c r="E51">
-        <v>-0.1702999999999997</v>
+        <v>-0.09499999999999975</v>
       </c>
       <c r="F51">
-        <v>3.6897</v>
+        <v>3.765</v>
       </c>
       <c r="G51">
         <v>0.981</v>
@@ -5463,45 +5463,45 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M51">
-        <v>0.23650977</v>
+        <v>0.2707035</v>
       </c>
       <c r="N51">
-        <v>0.4814902300000002</v>
+        <v>0.4472965000000002</v>
       </c>
       <c r="O51">
-        <v>0.07703843680000003</v>
+        <v>0.07156744000000004</v>
       </c>
       <c r="P51">
-        <v>0.4044517932000001</v>
+        <v>0.3757290600000002</v>
       </c>
       <c r="Q51">
-        <v>0.7014517932000002</v>
+        <v>0.6727290600000002</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1346233475079442</v>
+        <v>0.1362425231135578</v>
       </c>
       <c r="T51">
-        <v>1.222686811997444</v>
+        <v>1.24497537367448</v>
       </c>
       <c r="U51">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V51">
         <v>0.16</v>
       </c>
       <c r="W51">
-        <v>0.053844</v>
+        <v>0.06039600000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.035815391474103</v>
+        <v>2.652348418103203</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09831926155677888</v>
+        <v>0.09838657588450622</v>
       </c>
       <c r="C52">
-        <v>3.944550066590705</v>
+        <v>3.863878933113095</v>
       </c>
       <c r="D52">
-        <v>6.728550066590705</v>
+        <v>6.723178933113095</v>
       </c>
       <c r="E52">
-        <v>-0.09499999999999975</v>
+        <v>-0.01969999999999983</v>
       </c>
       <c r="F52">
-        <v>3.765</v>
+        <v>3.8403</v>
       </c>
       <c r="G52">
         <v>0.981</v>
@@ -5545,28 +5545,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M52">
-        <v>0.2707035</v>
+        <v>0.27611757</v>
       </c>
       <c r="N52">
-        <v>0.4472965000000002</v>
+        <v>0.4418824300000002</v>
       </c>
       <c r="O52">
-        <v>0.07156744000000004</v>
+        <v>0.07070118880000004</v>
       </c>
       <c r="P52">
-        <v>0.3757290600000002</v>
+        <v>0.3711812412000002</v>
       </c>
       <c r="Q52">
-        <v>0.6727290600000002</v>
+        <v>0.6681812412000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1362425231135578</v>
+        <v>0.1379277875194005</v>
       </c>
       <c r="T52">
-        <v>1.24497537367448</v>
+        <v>1.268173672562825</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.652348418103203</v>
+        <v>2.600341586375689</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09838657588450622</v>
+        <v>0.09845389021223357</v>
       </c>
       <c r="C53">
-        <v>3.863878933113095</v>
+        <v>3.783216367919545</v>
       </c>
       <c r="D53">
-        <v>6.723178933113095</v>
+        <v>6.717816367919545</v>
       </c>
       <c r="E53">
-        <v>-0.01969999999999983</v>
+        <v>0.05560000000000054</v>
       </c>
       <c r="F53">
-        <v>3.8403</v>
+        <v>3.9156</v>
       </c>
       <c r="G53">
         <v>0.981</v>
@@ -5627,28 +5627,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M53">
-        <v>0.27611757</v>
+        <v>0.28153164</v>
       </c>
       <c r="N53">
-        <v>0.4418824300000002</v>
+        <v>0.4364683600000002</v>
       </c>
       <c r="O53">
-        <v>0.07070118880000004</v>
+        <v>0.06983493760000002</v>
       </c>
       <c r="P53">
-        <v>0.3711812412000002</v>
+        <v>0.3666334224000001</v>
       </c>
       <c r="Q53">
-        <v>0.6681812412000001</v>
+        <v>0.6636334224000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1379277875194005</v>
+        <v>0.1396832712754866</v>
       </c>
       <c r="T53">
-        <v>1.268173672562825</v>
+        <v>1.292338567238184</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.600341586375689</v>
+        <v>2.550335017406925</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09845389021223357</v>
+        <v>0.09852120453996091</v>
       </c>
       <c r="C54">
-        <v>3.783216367919545</v>
+        <v>3.702562350523599</v>
       </c>
       <c r="D54">
-        <v>6.717816367919545</v>
+        <v>6.712462350523599</v>
       </c>
       <c r="E54">
-        <v>0.05560000000000054</v>
+        <v>0.1309000000000005</v>
       </c>
       <c r="F54">
-        <v>3.9156</v>
+        <v>3.9909</v>
       </c>
       <c r="G54">
         <v>0.981</v>
@@ -5709,28 +5709,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M54">
-        <v>0.28153164</v>
+        <v>0.28694571</v>
       </c>
       <c r="N54">
-        <v>0.4364683600000002</v>
+        <v>0.4310542900000002</v>
       </c>
       <c r="O54">
-        <v>0.06983493760000002</v>
+        <v>0.06896868640000003</v>
       </c>
       <c r="P54">
-        <v>0.3666334224000001</v>
+        <v>0.3620856036000001</v>
       </c>
       <c r="Q54">
-        <v>0.6636334224000001</v>
+        <v>0.6590856036000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1396832712754866</v>
+        <v>0.1415134564680019</v>
       </c>
       <c r="T54">
-        <v>1.292338567238184</v>
+        <v>1.317531755303983</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.550335017406925</v>
+        <v>2.502215488776605</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09852120453996091</v>
+        <v>0.1003575588676882</v>
       </c>
       <c r="C55">
-        <v>3.702562350523599</v>
+        <v>3.48442518857102</v>
       </c>
       <c r="D55">
-        <v>6.712462350523599</v>
+        <v>6.56962518857102</v>
       </c>
       <c r="E55">
-        <v>0.1309000000000005</v>
+        <v>0.2062000000000008</v>
       </c>
       <c r="F55">
-        <v>3.9909</v>
+        <v>4.0662</v>
       </c>
       <c r="G55">
         <v>0.981</v>
@@ -5791,45 +5791,45 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M55">
-        <v>0.28694571</v>
+        <v>0.3082179600000001</v>
       </c>
       <c r="N55">
-        <v>0.4310542900000002</v>
+        <v>0.4097820400000001</v>
       </c>
       <c r="O55">
-        <v>0.06896868640000003</v>
+        <v>0.06556512640000002</v>
       </c>
       <c r="P55">
-        <v>0.3620856036000001</v>
+        <v>0.3442169136000001</v>
       </c>
       <c r="Q55">
-        <v>0.6590856036000001</v>
+        <v>0.6412169136000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1415134564680019</v>
+        <v>0.143423214929757</v>
       </c>
       <c r="T55">
-        <v>1.317531755303983</v>
+        <v>1.343820299372643</v>
       </c>
       <c r="U55">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V55">
         <v>0.16</v>
       </c>
       <c r="W55">
-        <v>0.06039600000000001</v>
+        <v>0.06367200000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.502215488776605</v>
+        <v>2.329520317375406</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1003575588676882</v>
+        <v>0.1004576331954156</v>
       </c>
       <c r="C56">
-        <v>3.48442518857102</v>
+        <v>3.401515571465074</v>
       </c>
       <c r="D56">
-        <v>6.56962518857102</v>
+        <v>6.562015571465074</v>
       </c>
       <c r="E56">
-        <v>0.2062000000000008</v>
+        <v>0.2815000000000003</v>
       </c>
       <c r="F56">
-        <v>4.0662</v>
+        <v>4.1415</v>
       </c>
       <c r="G56">
         <v>0.981</v>
@@ -5873,28 +5873,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M56">
-        <v>0.3082179600000001</v>
+        <v>0.3139257</v>
       </c>
       <c r="N56">
-        <v>0.4097820400000001</v>
+        <v>0.4040743000000002</v>
       </c>
       <c r="O56">
-        <v>0.06556512640000002</v>
+        <v>0.06465188800000003</v>
       </c>
       <c r="P56">
-        <v>0.3442169136000001</v>
+        <v>0.3394224120000001</v>
       </c>
       <c r="Q56">
-        <v>0.6412169136000001</v>
+        <v>0.6364224120000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.143423214929757</v>
+        <v>0.145417851545368</v>
       </c>
       <c r="T56">
-        <v>1.343820299372643</v>
+        <v>1.371277223177689</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.329520317375406</v>
+        <v>2.287165402514034</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1004576331954156</v>
+        <v>0.1005577075231429</v>
       </c>
       <c r="C57">
-        <v>3.401515571465074</v>
+        <v>3.318623562449522</v>
       </c>
       <c r="D57">
-        <v>6.562015571465074</v>
+        <v>6.554423562449522</v>
       </c>
       <c r="E57">
-        <v>0.2815000000000003</v>
+        <v>0.3568000000000007</v>
       </c>
       <c r="F57">
-        <v>4.1415</v>
+        <v>4.2168</v>
       </c>
       <c r="G57">
         <v>0.981</v>
@@ -5955,28 +5955,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M57">
-        <v>0.3139257</v>
+        <v>0.31963344</v>
       </c>
       <c r="N57">
-        <v>0.4040743000000002</v>
+        <v>0.3983665600000001</v>
       </c>
       <c r="O57">
-        <v>0.06465188800000003</v>
+        <v>0.06373864960000003</v>
       </c>
       <c r="P57">
-        <v>0.3394224120000001</v>
+        <v>0.3346279104000001</v>
       </c>
       <c r="Q57">
-        <v>0.6364224120000002</v>
+        <v>0.6316279104000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.145417851545368</v>
+        <v>0.1475031534616885</v>
       </c>
       <c r="T57">
-        <v>1.371277223177689</v>
+        <v>1.399982188973872</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.287165402514034</v>
+        <v>2.246323163183427</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1005577075231429</v>
+        <v>0.1006577818508703</v>
       </c>
       <c r="C58">
-        <v>3.318623562449522</v>
+        <v>3.235749100479265</v>
       </c>
       <c r="D58">
-        <v>6.554423562449522</v>
+        <v>6.546849100479266</v>
       </c>
       <c r="E58">
-        <v>0.3568000000000007</v>
+        <v>0.432100000000001</v>
       </c>
       <c r="F58">
-        <v>4.2168</v>
+        <v>4.2921</v>
       </c>
       <c r="G58">
         <v>0.981</v>
@@ -6037,28 +6037,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M58">
-        <v>0.31963344</v>
+        <v>0.3253411800000001</v>
       </c>
       <c r="N58">
-        <v>0.3983665600000001</v>
+        <v>0.3926588200000001</v>
       </c>
       <c r="O58">
-        <v>0.06373864960000003</v>
+        <v>0.06282541120000003</v>
       </c>
       <c r="P58">
-        <v>0.3346279104000001</v>
+        <v>0.3298334088000001</v>
       </c>
       <c r="Q58">
-        <v>0.6316279104000001</v>
+        <v>0.6268334088</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1475031534616885</v>
+        <v>0.1496854461648146</v>
       </c>
       <c r="T58">
-        <v>1.399982188973872</v>
+        <v>1.430022269458251</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.246323163183427</v>
+        <v>2.206913984881963</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1006577818508703</v>
+        <v>0.1007578561785976</v>
       </c>
       <c r="C59">
-        <v>3.235749100479265</v>
+        <v>3.15289212479106</v>
       </c>
       <c r="D59">
-        <v>6.546849100479266</v>
+        <v>6.53929212479106</v>
       </c>
       <c r="E59">
-        <v>0.432100000000001</v>
+        <v>0.5074000000000005</v>
       </c>
       <c r="F59">
-        <v>4.2921</v>
+        <v>4.3674</v>
       </c>
       <c r="G59">
         <v>0.981</v>
@@ -6119,28 +6119,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M59">
-        <v>0.3253411800000001</v>
+        <v>0.33104892</v>
       </c>
       <c r="N59">
-        <v>0.3926588200000001</v>
+        <v>0.3869510800000002</v>
       </c>
       <c r="O59">
-        <v>0.06282541120000003</v>
+        <v>0.06191217280000003</v>
       </c>
       <c r="P59">
-        <v>0.3298334088000001</v>
+        <v>0.3250389072000002</v>
       </c>
       <c r="Q59">
-        <v>0.6268334088</v>
+        <v>0.6220389072000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1496854461648146</v>
+        <v>0.1519716575680896</v>
       </c>
       <c r="T59">
-        <v>1.430022269458251</v>
+        <v>1.461492829965694</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.206913984881963</v>
+        <v>2.168863743763309</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1007578561785976</v>
+        <v>0.100857930506325</v>
       </c>
       <c r="C60">
-        <v>3.152892124791061</v>
+        <v>3.070052574901894</v>
       </c>
       <c r="D60">
-        <v>6.53929212479106</v>
+        <v>6.531752574901893</v>
       </c>
       <c r="E60">
-        <v>0.5073999999999996</v>
+        <v>0.5827</v>
       </c>
       <c r="F60">
-        <v>4.367399999999999</v>
+        <v>4.442699999999999</v>
       </c>
       <c r="G60">
         <v>0.981</v>
@@ -6201,28 +6201,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M60">
-        <v>0.33104892</v>
+        <v>0.33675666</v>
       </c>
       <c r="N60">
-        <v>0.3869510800000002</v>
+        <v>0.3812433400000002</v>
       </c>
       <c r="O60">
-        <v>0.06191217280000004</v>
+        <v>0.06099893440000004</v>
       </c>
       <c r="P60">
-        <v>0.3250389072000002</v>
+        <v>0.3202444056000002</v>
       </c>
       <c r="Q60">
-        <v>0.6220389072000001</v>
+        <v>0.6172444056000002</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1519716575680895</v>
+        <v>0.1543693914788413</v>
       </c>
       <c r="T60">
-        <v>1.461492829965694</v>
+        <v>1.494498539766184</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.168863743763309</v>
+        <v>2.132103341326643</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.100857930506325</v>
+        <v>0.1009580048340523</v>
       </c>
       <c r="C61">
-        <v>3.070052574901894</v>
+        <v>2.987230390607371</v>
       </c>
       <c r="D61">
-        <v>6.531752574901893</v>
+        <v>6.524230390607371</v>
       </c>
       <c r="E61">
-        <v>0.5827</v>
+        <v>0.6580000000000004</v>
       </c>
       <c r="F61">
-        <v>4.442699999999999</v>
+        <v>4.518</v>
       </c>
       <c r="G61">
         <v>0.981</v>
@@ -6283,28 +6283,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M61">
-        <v>0.33675666</v>
+        <v>0.3424644</v>
       </c>
       <c r="N61">
-        <v>0.3812433400000002</v>
+        <v>0.3755356000000002</v>
       </c>
       <c r="O61">
-        <v>0.06099893440000004</v>
+        <v>0.06008569600000003</v>
       </c>
       <c r="P61">
-        <v>0.3202444056000002</v>
+        <v>0.3154499040000002</v>
       </c>
       <c r="Q61">
-        <v>0.6172444056000002</v>
+        <v>0.6124499040000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1543693914788413</v>
+        <v>0.1568870120851307</v>
       </c>
       <c r="T61">
-        <v>1.494498539766184</v>
+        <v>1.529154535056698</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.132103341326643</v>
+        <v>2.096568285637865</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1009580048340523</v>
+        <v>0.1010580791617796</v>
       </c>
       <c r="C62">
-        <v>2.987230390607371</v>
+        <v>2.904425511980111</v>
       </c>
       <c r="D62">
-        <v>6.524230390607371</v>
+        <v>6.51672551198011</v>
       </c>
       <c r="E62">
-        <v>0.6580000000000004</v>
+        <v>0.7332999999999998</v>
       </c>
       <c r="F62">
-        <v>4.518</v>
+        <v>4.593299999999999</v>
       </c>
       <c r="G62">
         <v>0.981</v>
@@ -6365,28 +6365,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M62">
-        <v>0.3424644</v>
+        <v>0.34817214</v>
       </c>
       <c r="N62">
-        <v>0.3755356000000002</v>
+        <v>0.3698278600000002</v>
       </c>
       <c r="O62">
-        <v>0.06008569600000003</v>
+        <v>0.05917245760000004</v>
       </c>
       <c r="P62">
-        <v>0.3154499040000002</v>
+        <v>0.3106554024000002</v>
       </c>
       <c r="Q62">
-        <v>0.6124499040000002</v>
+        <v>0.6076554024000002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1568870120851307</v>
+        <v>0.1595337414404606</v>
       </c>
       <c r="T62">
-        <v>1.529154535056698</v>
+        <v>1.565587760874932</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.096568285637865</v>
+        <v>2.062198313742163</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1010580791617796</v>
+        <v>0.101158153489507</v>
       </c>
       <c r="C63">
-        <v>2.904425511980111</v>
+        <v>2.821637879368155</v>
       </c>
       <c r="D63">
-        <v>6.51672551198011</v>
+        <v>6.509237879368155</v>
       </c>
       <c r="E63">
-        <v>0.7332999999999998</v>
+        <v>0.8086000000000002</v>
       </c>
       <c r="F63">
-        <v>4.593299999999999</v>
+        <v>4.6686</v>
       </c>
       <c r="G63">
         <v>0.981</v>
@@ -6447,28 +6447,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M63">
-        <v>0.34817214</v>
+        <v>0.35387988</v>
       </c>
       <c r="N63">
-        <v>0.3698278600000002</v>
+        <v>0.3641201200000002</v>
       </c>
       <c r="O63">
-        <v>0.05917245760000004</v>
+        <v>0.05825921920000004</v>
       </c>
       <c r="P63">
-        <v>0.3106554024000002</v>
+        <v>0.3058609008000002</v>
       </c>
       <c r="Q63">
-        <v>0.6076554024000002</v>
+        <v>0.6028609008000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1595337414404606</v>
+        <v>0.1623197723408078</v>
       </c>
       <c r="T63">
-        <v>1.565587760874932</v>
+        <v>1.603938524894124</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.062198313742163</v>
+        <v>2.028937050617289</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.101158153489507</v>
+        <v>0.1087728678172343</v>
       </c>
       <c r="C64">
-        <v>2.821637879368155</v>
+        <v>2.223007403173684</v>
       </c>
       <c r="D64">
-        <v>6.509237879368155</v>
+        <v>5.985907403173684</v>
       </c>
       <c r="E64">
-        <v>0.8086000000000002</v>
+        <v>0.8839000000000006</v>
       </c>
       <c r="F64">
-        <v>4.6686</v>
+        <v>4.7439</v>
       </c>
       <c r="G64">
         <v>0.981</v>
@@ -6529,45 +6529,45 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M64">
-        <v>0.35387988</v>
+        <v>0.426951</v>
       </c>
       <c r="N64">
-        <v>0.3641201200000002</v>
+        <v>0.2910490000000002</v>
       </c>
       <c r="O64">
-        <v>0.05825921920000004</v>
+        <v>0.04656784000000003</v>
       </c>
       <c r="P64">
-        <v>0.3058609008000002</v>
+        <v>0.2444811600000002</v>
       </c>
       <c r="Q64">
-        <v>0.6028609008000001</v>
+        <v>0.5414811600000002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1623197723408078</v>
+        <v>0.1652563995060387</v>
       </c>
       <c r="T64">
-        <v>1.603938524894124</v>
+        <v>1.644362303184625</v>
       </c>
       <c r="U64">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V64">
         <v>0.16</v>
       </c>
       <c r="W64">
-        <v>0.06367200000000001</v>
+        <v>0.0756</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.028937050617289</v>
+        <v>1.681691810067198</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1087728678172343</v>
+        <v>0.1089922221449617</v>
       </c>
       <c r="C65">
-        <v>2.223007403173684</v>
+        <v>2.133876077505311</v>
       </c>
       <c r="D65">
-        <v>5.985907403173684</v>
+        <v>5.972076077505311</v>
       </c>
       <c r="E65">
-        <v>0.8839000000000006</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="F65">
-        <v>4.7439</v>
+        <v>4.819199999999999</v>
       </c>
       <c r="G65">
         <v>0.981</v>
@@ -6611,28 +6611,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M65">
-        <v>0.426951</v>
+        <v>0.4337279999999999</v>
       </c>
       <c r="N65">
-        <v>0.2910490000000002</v>
+        <v>0.2842720000000002</v>
       </c>
       <c r="O65">
-        <v>0.04656784000000003</v>
+        <v>0.04548352000000004</v>
       </c>
       <c r="P65">
-        <v>0.2444811600000002</v>
+        <v>0.2387884800000002</v>
       </c>
       <c r="Q65">
-        <v>0.5414811600000002</v>
+        <v>0.5357884800000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1652563995060387</v>
+        <v>0.1683561726248935</v>
       </c>
       <c r="T65">
-        <v>1.644362303184625</v>
+        <v>1.687031846935709</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.681691810067198</v>
+        <v>1.655415375534898</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1089922221449617</v>
+        <v>0.109211576472689</v>
       </c>
       <c r="C66">
-        <v>2.133876077505311</v>
+        <v>2.044808523137118</v>
       </c>
       <c r="D66">
-        <v>5.972076077505311</v>
+        <v>5.958308523137118</v>
       </c>
       <c r="E66">
-        <v>0.9592000000000001</v>
+        <v>1.0345</v>
       </c>
       <c r="F66">
-        <v>4.819199999999999</v>
+        <v>4.8945</v>
       </c>
       <c r="G66">
         <v>0.981</v>
@@ -6693,28 +6693,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M66">
-        <v>0.4337279999999999</v>
+        <v>0.440505</v>
       </c>
       <c r="N66">
-        <v>0.2842720000000002</v>
+        <v>0.2774950000000002</v>
       </c>
       <c r="O66">
-        <v>0.04548352000000004</v>
+        <v>0.04439920000000003</v>
       </c>
       <c r="P66">
-        <v>0.2387884800000002</v>
+        <v>0.2330958000000002</v>
       </c>
       <c r="Q66">
-        <v>0.5357884800000001</v>
+        <v>0.5300958000000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1683561726248935</v>
+        <v>0.1716330756362543</v>
       </c>
       <c r="T66">
-        <v>1.687031846935709</v>
+        <v>1.732139650329712</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.655415375534898</v>
+        <v>1.629947446680515</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.109211576472689</v>
+        <v>0.1094309308004163</v>
       </c>
       <c r="C67">
-        <v>2.044808523137118</v>
+        <v>1.955804300043493</v>
       </c>
       <c r="D67">
-        <v>5.958308523137118</v>
+        <v>5.944604300043493</v>
       </c>
       <c r="E67">
-        <v>1.0345</v>
+        <v>1.109800000000001</v>
       </c>
       <c r="F67">
-        <v>4.8945</v>
+        <v>4.9698</v>
       </c>
       <c r="G67">
         <v>0.981</v>
@@ -6775,28 +6775,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M67">
-        <v>0.440505</v>
+        <v>0.447282</v>
       </c>
       <c r="N67">
-        <v>0.2774950000000002</v>
+        <v>0.2707180000000002</v>
       </c>
       <c r="O67">
-        <v>0.04439920000000003</v>
+        <v>0.04331488000000003</v>
       </c>
       <c r="P67">
-        <v>0.2330958000000002</v>
+        <v>0.2274031200000002</v>
       </c>
       <c r="Q67">
-        <v>0.5300958000000002</v>
+        <v>0.5244031200000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1716330756362543</v>
+        <v>0.1751027376482834</v>
       </c>
       <c r="T67">
-        <v>1.732139650329712</v>
+        <v>1.779900853923362</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.629947446680515</v>
+        <v>1.605251273245961</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1094309308004163</v>
+        <v>0.1096502851281437</v>
       </c>
       <c r="C68">
-        <v>1.955804300043493</v>
+        <v>1.866862972237798</v>
       </c>
       <c r="D68">
-        <v>5.944604300043493</v>
+        <v>5.930962972237798</v>
       </c>
       <c r="E68">
-        <v>1.109800000000001</v>
+        <v>1.1851</v>
       </c>
       <c r="F68">
-        <v>4.9698</v>
+        <v>5.0451</v>
       </c>
       <c r="G68">
         <v>0.981</v>
@@ -6857,28 +6857,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M68">
-        <v>0.447282</v>
+        <v>0.4540589999999999</v>
       </c>
       <c r="N68">
-        <v>0.2707180000000002</v>
+        <v>0.2639410000000003</v>
       </c>
       <c r="O68">
-        <v>0.04331488000000003</v>
+        <v>0.04223056000000004</v>
       </c>
       <c r="P68">
-        <v>0.2274031200000002</v>
+        <v>0.2217104400000002</v>
       </c>
       <c r="Q68">
-        <v>0.5244031200000001</v>
+        <v>0.5187104400000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1751027376482834</v>
+        <v>0.178782682206496</v>
       </c>
       <c r="T68">
-        <v>1.779900853923362</v>
+        <v>1.830556675916628</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.605251273245961</v>
+        <v>1.58129229901841</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1096502851281437</v>
+        <v>0.109869639455871</v>
       </c>
       <c r="C69">
-        <v>1.866862972237798</v>
+        <v>1.777984107726142</v>
       </c>
       <c r="D69">
-        <v>5.930962972237798</v>
+        <v>5.917384107726142</v>
       </c>
       <c r="E69">
-        <v>1.1851</v>
+        <v>1.260400000000001</v>
       </c>
       <c r="F69">
-        <v>5.0451</v>
+        <v>5.1204</v>
       </c>
       <c r="G69">
         <v>0.981</v>
@@ -6939,28 +6939,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M69">
-        <v>0.4540589999999999</v>
+        <v>0.460836</v>
       </c>
       <c r="N69">
-        <v>0.2639410000000003</v>
+        <v>0.2571640000000002</v>
       </c>
       <c r="O69">
-        <v>0.04223056000000004</v>
+        <v>0.04114624000000004</v>
       </c>
       <c r="P69">
-        <v>0.2217104400000002</v>
+        <v>0.2160177600000002</v>
       </c>
       <c r="Q69">
-        <v>0.5187104400000002</v>
+        <v>0.5130177600000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.178782682206496</v>
+        <v>0.182692623299597</v>
       </c>
       <c r="T69">
-        <v>1.830556675916628</v>
+        <v>1.884378486784472</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.58129229901841</v>
+        <v>1.558038000503434</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.109869639455871</v>
+        <v>0.1100889937835983</v>
       </c>
       <c r="C70">
-        <v>1.777984107726142</v>
+        <v>1.689167278461773</v>
       </c>
       <c r="D70">
-        <v>5.917384107726142</v>
+        <v>5.903867278461774</v>
       </c>
       <c r="E70">
-        <v>1.260400000000001</v>
+        <v>1.335700000000001</v>
       </c>
       <c r="F70">
-        <v>5.1204</v>
+        <v>5.1957</v>
       </c>
       <c r="G70">
         <v>0.981</v>
@@ -7021,28 +7021,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M70">
-        <v>0.460836</v>
+        <v>0.467613</v>
       </c>
       <c r="N70">
-        <v>0.2571640000000002</v>
+        <v>0.2503870000000002</v>
       </c>
       <c r="O70">
-        <v>0.04114624000000004</v>
+        <v>0.04006192000000003</v>
       </c>
       <c r="P70">
-        <v>0.2160177600000002</v>
+        <v>0.2103250800000002</v>
       </c>
       <c r="Q70">
-        <v>0.5130177600000002</v>
+        <v>0.5073250800000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.182692623299597</v>
+        <v>0.1868548186567689</v>
       </c>
       <c r="T70">
-        <v>1.884378486784472</v>
+        <v>1.941672672547016</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.558038000503434</v>
+        <v>1.535457739626572</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1100889937835983</v>
+        <v>0.1103083481113257</v>
       </c>
       <c r="C71">
-        <v>1.689167278461773</v>
+        <v>1.600412060300102</v>
       </c>
       <c r="D71">
-        <v>5.903867278461774</v>
+        <v>5.890412060300102</v>
       </c>
       <c r="E71">
-        <v>1.335700000000001</v>
+        <v>1.411</v>
       </c>
       <c r="F71">
-        <v>5.1957</v>
+        <v>5.271</v>
       </c>
       <c r="G71">
         <v>0.981</v>
@@ -7103,28 +7103,28 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M71">
-        <v>0.467613</v>
+        <v>0.47439</v>
       </c>
       <c r="N71">
-        <v>0.2503870000000002</v>
+        <v>0.2436100000000002</v>
       </c>
       <c r="O71">
-        <v>0.04006192000000003</v>
+        <v>0.03897760000000004</v>
       </c>
       <c r="P71">
-        <v>0.2103250800000002</v>
+        <v>0.2046324000000002</v>
       </c>
       <c r="Q71">
-        <v>0.5073250800000002</v>
+        <v>0.5016324000000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1868548186567689</v>
+        <v>0.191294493704419</v>
       </c>
       <c r="T71">
-        <v>1.941672672547016</v>
+        <v>2.002786470693729</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.535457739626572</v>
+        <v>1.513522629060478</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1103083481113257</v>
+        <v>0.1462989153435097</v>
       </c>
       <c r="C72">
-        <v>1.600412060300102</v>
+        <v>-0.07804469300780781</v>
       </c>
       <c r="D72">
-        <v>5.890412060300102</v>
+        <v>4.287255306992193</v>
       </c>
       <c r="E72">
-        <v>1.411</v>
+        <v>1.486300000000001</v>
       </c>
       <c r="F72">
-        <v>5.271</v>
+        <v>5.3463</v>
       </c>
       <c r="G72">
         <v>0.981</v>
@@ -7185,45 +7185,45 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M72">
-        <v>0.47439</v>
+        <v>0.7848368400000001</v>
       </c>
       <c r="N72">
-        <v>0.2436100000000002</v>
+        <v>-0.0668368399999999</v>
       </c>
       <c r="O72">
-        <v>0.03897760000000004</v>
+        <v>-0.01069389439999998</v>
       </c>
       <c r="P72">
-        <v>0.2046324000000002</v>
+        <v>-0.05614294559999991</v>
       </c>
       <c r="Q72">
-        <v>0.5016324000000002</v>
+        <v>0.2408570544000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.191294493704419</v>
+        <v>0.1976800808428943</v>
       </c>
       <c r="T72">
-        <v>2.002786470693729</v>
+        <v>2.090686481221658</v>
       </c>
       <c r="U72">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.16</v>
+        <v>0.1463743725383737</v>
       </c>
       <c r="W72">
-        <v>0.0756</v>
+        <v>0.1253122421113667</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y72">
-        <v>1.513522629060478</v>
+        <v>0.9148398283648358</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1462989153435097</v>
+        <v>0.1473089153435097</v>
       </c>
       <c r="C73">
-        <v>-0.07804469300780603</v>
+        <v>-0.1858412934161615</v>
       </c>
       <c r="D73">
-        <v>4.287255306992193</v>
+        <v>4.254758706583838</v>
       </c>
       <c r="E73">
-        <v>1.4863</v>
+        <v>1.5616</v>
       </c>
       <c r="F73">
-        <v>5.346299999999999</v>
+        <v>5.4216</v>
       </c>
       <c r="G73">
         <v>0.981</v>
@@ -7267,37 +7267,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M73">
-        <v>0.78483684</v>
+        <v>0.7958908800000001</v>
       </c>
       <c r="N73">
-        <v>-0.06683683999999979</v>
+        <v>-0.07789087999999988</v>
       </c>
       <c r="O73">
-        <v>-0.01069389439999997</v>
+        <v>-0.01246254079999998</v>
       </c>
       <c r="P73">
-        <v>-0.05614294559999982</v>
+        <v>-0.06542833919999991</v>
       </c>
       <c r="Q73">
-        <v>0.2408570544000002</v>
+        <v>0.2315716608000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1976800808428942</v>
+        <v>0.2031043694444262</v>
       </c>
       <c r="T73">
-        <v>2.090686481221657</v>
+        <v>2.165353855551003</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.1463743725383737</v>
+        <v>0.1443413951420074</v>
       </c>
       <c r="W73">
-        <v>0.1253122421113667</v>
+        <v>0.1256106831931533</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.9148398283648359</v>
+        <v>0.9021337196375464</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1473089153435097</v>
+        <v>0.1483189153435097</v>
       </c>
       <c r="C74">
-        <v>-0.1858412934161615</v>
+        <v>-0.2931489634133539</v>
       </c>
       <c r="D74">
-        <v>4.254758706583838</v>
+        <v>4.222751036586645</v>
       </c>
       <c r="E74">
-        <v>1.5616</v>
+        <v>1.6369</v>
       </c>
       <c r="F74">
-        <v>5.4216</v>
+        <v>5.496899999999999</v>
       </c>
       <c r="G74">
         <v>0.981</v>
@@ -7349,37 +7349,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M74">
-        <v>0.7958908800000001</v>
+        <v>0.80694492</v>
       </c>
       <c r="N74">
-        <v>-0.07789087999999988</v>
+        <v>-0.08894491999999976</v>
       </c>
       <c r="O74">
-        <v>-0.01246254079999998</v>
+        <v>-0.01423118719999996</v>
       </c>
       <c r="P74">
-        <v>-0.06542833919999991</v>
+        <v>-0.07471373279999979</v>
       </c>
       <c r="Q74">
-        <v>0.2315716608000001</v>
+        <v>0.2222862672000002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2031043694444262</v>
+        <v>0.2089304572016271</v>
       </c>
       <c r="T74">
-        <v>2.165353855551003</v>
+        <v>2.245552146497336</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.1443413951420074</v>
+        <v>0.1423641157565005</v>
       </c>
       <c r="W74">
-        <v>0.1256106831931533</v>
+        <v>0.1259009478069457</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9021337196375464</v>
+        <v>0.8897757234781282</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1483189153435097</v>
+        <v>0.1493289153435097</v>
       </c>
       <c r="C75">
-        <v>-0.2931489634133539</v>
+        <v>-0.3999786549770832</v>
       </c>
       <c r="D75">
-        <v>4.222751036586645</v>
+        <v>4.191221345022917</v>
       </c>
       <c r="E75">
-        <v>1.6369</v>
+        <v>1.7122</v>
       </c>
       <c r="F75">
-        <v>5.496899999999999</v>
+        <v>5.5722</v>
       </c>
       <c r="G75">
         <v>0.981</v>
@@ -7431,37 +7431,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M75">
-        <v>0.80694492</v>
+        <v>0.8179989600000001</v>
       </c>
       <c r="N75">
-        <v>-0.08894491999999976</v>
+        <v>-0.09999895999999986</v>
       </c>
       <c r="O75">
-        <v>-0.01423118719999996</v>
+        <v>-0.01599983359999998</v>
       </c>
       <c r="P75">
-        <v>-0.07471373279999979</v>
+        <v>-0.08399912639999987</v>
       </c>
       <c r="Q75">
-        <v>0.2222862672000002</v>
+        <v>0.2130008736000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2089304572016271</v>
+        <v>0.2152047055555358</v>
       </c>
       <c r="T75">
-        <v>2.245552146497336</v>
+        <v>2.331919536747233</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1423641157565005</v>
+        <v>0.1404402763543856</v>
       </c>
       <c r="W75">
-        <v>0.1259009478069457</v>
+        <v>0.1261833674311762</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8897757234781282</v>
+        <v>0.8777517272149101</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1493289153435097</v>
+        <v>0.1503389153435097</v>
       </c>
       <c r="C76">
-        <v>-0.3999786549770832</v>
+        <v>-0.5063409954120885</v>
       </c>
       <c r="D76">
-        <v>4.191221345022917</v>
+        <v>4.160159004587911</v>
       </c>
       <c r="E76">
-        <v>1.7122</v>
+        <v>1.7875</v>
       </c>
       <c r="F76">
-        <v>5.5722</v>
+        <v>5.647499999999999</v>
       </c>
       <c r="G76">
         <v>0.981</v>
@@ -7513,37 +7513,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M76">
-        <v>0.8179989600000001</v>
+        <v>0.8290529999999999</v>
       </c>
       <c r="N76">
-        <v>-0.09999895999999986</v>
+        <v>-0.1110529999999997</v>
       </c>
       <c r="O76">
-        <v>-0.01599983359999998</v>
+        <v>-0.01776847999999996</v>
       </c>
       <c r="P76">
-        <v>-0.08399912639999987</v>
+        <v>-0.09328451999999977</v>
       </c>
       <c r="Q76">
-        <v>0.2130008736000001</v>
+        <v>0.2037154800000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2152047055555358</v>
+        <v>0.2219808937777573</v>
       </c>
       <c r="T76">
-        <v>2.331919536747233</v>
+        <v>2.425196318217123</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1404402763543856</v>
+        <v>0.1385677393363272</v>
       </c>
       <c r="W76">
-        <v>0.1261833674311762</v>
+        <v>0.1264582558654272</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8777517272149101</v>
+        <v>0.8660483708520448</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1503389153435097</v>
+        <v>0.1513489153435097</v>
       </c>
       <c r="C77">
-        <v>-0.5063409954120885</v>
+        <v>-0.6122462992928615</v>
       </c>
       <c r="D77">
-        <v>4.160159004587911</v>
+        <v>4.129553700707138</v>
       </c>
       <c r="E77">
-        <v>1.7875</v>
+        <v>1.8628</v>
       </c>
       <c r="F77">
-        <v>5.647499999999999</v>
+        <v>5.722799999999999</v>
       </c>
       <c r="G77">
         <v>0.981</v>
@@ -7595,37 +7595,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M77">
-        <v>0.8290529999999999</v>
+        <v>0.84010704</v>
       </c>
       <c r="N77">
-        <v>-0.1110529999999997</v>
+        <v>-0.1221070399999998</v>
       </c>
       <c r="O77">
-        <v>-0.01776847999999996</v>
+        <v>-0.01953712639999997</v>
       </c>
       <c r="P77">
-        <v>-0.09328451999999977</v>
+        <v>-0.1025699135999999</v>
       </c>
       <c r="Q77">
-        <v>0.2037154800000002</v>
+        <v>0.1944300864000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2219808937777573</v>
+        <v>0.2293217643518305</v>
       </c>
       <c r="T77">
-        <v>2.425196318217123</v>
+        <v>2.526246164809503</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1385677393363272</v>
+        <v>0.1367444796082176</v>
       </c>
       <c r="W77">
-        <v>0.1264582558654272</v>
+        <v>0.1267259103935137</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8660483708520448</v>
+        <v>0.8546529975513598</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1513489153435097</v>
+        <v>0.1523589153435097</v>
       </c>
       <c r="C78">
-        <v>-0.6122462992928615</v>
+        <v>-0.7177045798830415</v>
       </c>
       <c r="D78">
-        <v>4.129553700707138</v>
+        <v>4.099395420116958</v>
       </c>
       <c r="E78">
-        <v>1.8628</v>
+        <v>1.9381</v>
       </c>
       <c r="F78">
-        <v>5.722799999999999</v>
+        <v>5.7981</v>
       </c>
       <c r="G78">
         <v>0.981</v>
@@ -7677,37 +7677,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M78">
-        <v>0.84010704</v>
+        <v>0.85116108</v>
       </c>
       <c r="N78">
-        <v>-0.1221070399999998</v>
+        <v>-0.1331610799999998</v>
       </c>
       <c r="O78">
-        <v>-0.01953712639999997</v>
+        <v>-0.02130577279999997</v>
       </c>
       <c r="P78">
-        <v>-0.1025699135999999</v>
+        <v>-0.1118553071999999</v>
       </c>
       <c r="Q78">
-        <v>0.1944300864000001</v>
+        <v>0.1851446928000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2293217643518305</v>
+        <v>0.2373009714975623</v>
       </c>
       <c r="T78">
-        <v>2.526246164809503</v>
+        <v>2.636082954583829</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1367444796082176</v>
+        <v>0.1349685772756433</v>
       </c>
       <c r="W78">
-        <v>0.1267259103935137</v>
+        <v>0.1269866128559356</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8546529975513598</v>
+        <v>0.8435536079727708</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1523589153435097</v>
+        <v>0.1533689153435097</v>
       </c>
       <c r="C79">
-        <v>-0.7177045798830415</v>
+        <v>-0.8227255600580747</v>
       </c>
       <c r="D79">
-        <v>4.099395420116958</v>
+        <v>4.069674439941925</v>
       </c>
       <c r="E79">
-        <v>1.9381</v>
+        <v>2.0134</v>
       </c>
       <c r="F79">
-        <v>5.7981</v>
+        <v>5.873399999999999</v>
       </c>
       <c r="G79">
         <v>0.981</v>
@@ -7759,37 +7759,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M79">
-        <v>0.85116108</v>
+        <v>0.86221512</v>
       </c>
       <c r="N79">
-        <v>-0.1331610799999998</v>
+        <v>-0.1442151199999998</v>
       </c>
       <c r="O79">
-        <v>-0.02130577279999997</v>
+        <v>-0.02307441919999997</v>
       </c>
       <c r="P79">
-        <v>-0.1118553071999999</v>
+        <v>-0.1211407007999998</v>
       </c>
       <c r="Q79">
-        <v>0.1851446928000001</v>
+        <v>0.1758592992000002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2373009714975623</v>
+        <v>0.2460055611110878</v>
       </c>
       <c r="T79">
-        <v>2.636082954583829</v>
+        <v>2.755904907064912</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1349685772756433</v>
+        <v>0.1332382109003146</v>
       </c>
       <c r="W79">
-        <v>0.1269866128559356</v>
+        <v>0.1272406306398338</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8435536079727708</v>
+        <v>0.832738818126966</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1533689153435097</v>
+        <v>0.1543789153435097</v>
       </c>
       <c r="C80">
-        <v>-0.8227255600580747</v>
+        <v>-0.9273186827561428</v>
       </c>
       <c r="D80">
-        <v>4.069674439941925</v>
+        <v>4.040381317243857</v>
       </c>
       <c r="E80">
-        <v>2.0134</v>
+        <v>2.0887</v>
       </c>
       <c r="F80">
-        <v>5.873399999999999</v>
+        <v>5.9487</v>
       </c>
       <c r="G80">
         <v>0.981</v>
@@ -7841,37 +7841,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M80">
-        <v>0.86221512</v>
+        <v>0.87326916</v>
       </c>
       <c r="N80">
-        <v>-0.1442151199999998</v>
+        <v>-0.1552691599999998</v>
       </c>
       <c r="O80">
-        <v>-0.02307441919999997</v>
+        <v>-0.02484306559999997</v>
       </c>
       <c r="P80">
-        <v>-0.1211407007999998</v>
+        <v>-0.1304260943999998</v>
       </c>
       <c r="Q80">
-        <v>0.1758592992000002</v>
+        <v>0.1665739056000002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2460055611110878</v>
+        <v>0.2555391592592349</v>
       </c>
       <c r="T80">
-        <v>2.755904907064912</v>
+        <v>2.887138474068004</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1332382109003146</v>
+        <v>0.131551651268665</v>
       </c>
       <c r="W80">
-        <v>0.1272406306398338</v>
+        <v>0.12748821759376</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.832738818126966</v>
+        <v>0.8221978204291563</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1543789153435097</v>
+        <v>0.1553889153435097</v>
       </c>
       <c r="C81">
-        <v>-0.9273186827561428</v>
+        <v>-1.031493120980965</v>
       </c>
       <c r="D81">
-        <v>4.040381317243857</v>
+        <v>4.011506879019035</v>
       </c>
       <c r="E81">
-        <v>2.0887</v>
+        <v>2.164000000000001</v>
       </c>
       <c r="F81">
-        <v>5.9487</v>
+        <v>6.024</v>
       </c>
       <c r="G81">
         <v>0.981</v>
@@ -7923,37 +7923,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M81">
-        <v>0.87326916</v>
+        <v>0.8843232000000001</v>
       </c>
       <c r="N81">
-        <v>-0.1552691599999998</v>
+        <v>-0.1663231999999999</v>
       </c>
       <c r="O81">
-        <v>-0.02484306559999997</v>
+        <v>-0.02661171199999998</v>
       </c>
       <c r="P81">
-        <v>-0.1304260943999998</v>
+        <v>-0.1397114879999999</v>
       </c>
       <c r="Q81">
-        <v>0.1665739056000002</v>
+        <v>0.1572885120000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2555391592592349</v>
+        <v>0.2660261172221967</v>
       </c>
       <c r="T81">
-        <v>2.887138474068004</v>
+        <v>3.031495397771404</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.131551651268665</v>
+        <v>0.1299072556278067</v>
       </c>
       <c r="W81">
-        <v>0.12748821759376</v>
+        <v>0.127729614873838</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8221978204291563</v>
+        <v>0.8119203476737918</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1553889153435097</v>
+        <v>0.1563989153435097</v>
       </c>
       <c r="C82">
-        <v>-1.031493120980965</v>
+        <v>-1.135257787378751</v>
       </c>
       <c r="D82">
-        <v>4.011506879019035</v>
+        <v>3.983042212621249</v>
       </c>
       <c r="E82">
-        <v>2.164000000000001</v>
+        <v>2.2393</v>
       </c>
       <c r="F82">
-        <v>6.024</v>
+        <v>6.099299999999999</v>
       </c>
       <c r="G82">
         <v>0.981</v>
@@ -8005,37 +8005,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M82">
-        <v>0.8843232000000001</v>
+        <v>0.89537724</v>
       </c>
       <c r="N82">
-        <v>-0.1663231999999999</v>
+        <v>-0.1773772399999998</v>
       </c>
       <c r="O82">
-        <v>-0.02661171199999998</v>
+        <v>-0.02838035839999997</v>
       </c>
       <c r="P82">
-        <v>-0.1397114879999999</v>
+        <v>-0.1489968815999998</v>
       </c>
       <c r="Q82">
-        <v>0.1572885120000001</v>
+        <v>0.1480031184000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2660261172221967</v>
+        <v>0.2776169654970491</v>
       </c>
       <c r="T82">
-        <v>3.031495397771404</v>
+        <v>3.191047787127794</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1299072556278067</v>
+        <v>0.1283034623484511</v>
       </c>
       <c r="W82">
-        <v>0.127729614873838</v>
+        <v>0.1279650517272474</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8119203476737918</v>
+        <v>0.8018966396778192</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1563989153435097</v>
+        <v>0.2030626672020879</v>
       </c>
       <c r="C83">
-        <v>-1.135257787378751</v>
+        <v>-2.19395111949578</v>
       </c>
       <c r="D83">
-        <v>3.983042212621249</v>
+        <v>2.99964888050422</v>
       </c>
       <c r="E83">
-        <v>2.2393</v>
+        <v>2.3146</v>
       </c>
       <c r="F83">
-        <v>6.099299999999999</v>
+        <v>6.1746</v>
       </c>
       <c r="G83">
         <v>0.981</v>
@@ -8087,45 +8087,45 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M83">
-        <v>0.89537724</v>
+        <v>1.23985968</v>
       </c>
       <c r="N83">
-        <v>-0.1773772399999998</v>
+        <v>-0.5218596799999997</v>
       </c>
       <c r="O83">
-        <v>-0.02838035839999997</v>
+        <v>-0.08349754879999996</v>
       </c>
       <c r="P83">
-        <v>-0.1489968815999998</v>
+        <v>-0.4383621311999998</v>
       </c>
       <c r="Q83">
-        <v>0.1480031184000002</v>
+        <v>-0.1413621311999998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2776169654970491</v>
+        <v>0.2981276405723199</v>
       </c>
       <c r="T83">
-        <v>3.191047787127794</v>
+        <v>3.473384949859196</v>
       </c>
       <c r="U83">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1283034623484511</v>
+        <v>0.09265564632281617</v>
       </c>
       <c r="W83">
-        <v>0.1279650517272474</v>
+        <v>0.1821947462183785</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.8018966396778192</v>
+        <v>0.579097789517601</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2030626672020879</v>
+        <v>0.204612667202088</v>
       </c>
       <c r="C84">
-        <v>-2.19395111949578</v>
+        <v>-2.293651000710182</v>
       </c>
       <c r="D84">
-        <v>2.99964888050422</v>
+        <v>2.975248999289819</v>
       </c>
       <c r="E84">
-        <v>2.3146</v>
+        <v>2.389900000000001</v>
       </c>
       <c r="F84">
-        <v>6.1746</v>
+        <v>6.2499</v>
       </c>
       <c r="G84">
         <v>0.981</v>
@@ -8169,37 +8169,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M84">
-        <v>1.23985968</v>
+        <v>1.25497992</v>
       </c>
       <c r="N84">
-        <v>-0.5218596799999997</v>
+        <v>-0.5369799199999998</v>
       </c>
       <c r="O84">
-        <v>-0.08349754879999996</v>
+        <v>-0.08591678719999997</v>
       </c>
       <c r="P84">
-        <v>-0.4383621311999998</v>
+        <v>-0.4510631327999999</v>
       </c>
       <c r="Q84">
-        <v>-0.1413621311999998</v>
+        <v>-0.1540631327999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2981276405723199</v>
+        <v>0.3129704429589271</v>
       </c>
       <c r="T84">
-        <v>3.473384949859196</v>
+        <v>3.67770171161562</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.09265564632281617</v>
+        <v>0.09153931323458947</v>
       </c>
       <c r="W84">
-        <v>0.1821947462183785</v>
+        <v>0.1824189059024945</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.579097789517601</v>
+        <v>0.5721207077161842</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.204612667202088</v>
+        <v>0.206162667202088</v>
       </c>
       <c r="C85">
-        <v>-2.293651000710182</v>
+        <v>-2.392957135493762</v>
       </c>
       <c r="D85">
-        <v>2.975248999289819</v>
+        <v>2.951242864506237</v>
       </c>
       <c r="E85">
-        <v>2.389900000000001</v>
+        <v>2.4652</v>
       </c>
       <c r="F85">
-        <v>6.2499</v>
+        <v>6.3252</v>
       </c>
       <c r="G85">
         <v>0.981</v>
@@ -8251,37 +8251,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M85">
-        <v>1.25497992</v>
+        <v>1.27010016</v>
       </c>
       <c r="N85">
-        <v>-0.5369799199999998</v>
+        <v>-0.5521001599999997</v>
       </c>
       <c r="O85">
-        <v>-0.08591678719999997</v>
+        <v>-0.08833602559999996</v>
       </c>
       <c r="P85">
-        <v>-0.4510631327999999</v>
+        <v>-0.4637641343999998</v>
       </c>
       <c r="Q85">
-        <v>-0.1540631327999999</v>
+        <v>-0.1667641343999998</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3129704429589271</v>
+        <v>0.3296685956438601</v>
       </c>
       <c r="T85">
-        <v>3.67770171161562</v>
+        <v>3.907558068591597</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.09153931323458947</v>
+        <v>0.09044955950560626</v>
       </c>
       <c r="W85">
-        <v>0.1824189059024945</v>
+        <v>0.1826377284512743</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5721207077161842</v>
+        <v>0.5653097469100392</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.206162667202088</v>
+        <v>0.207712667202088</v>
       </c>
       <c r="C86">
-        <v>-2.392957135493761</v>
+        <v>-2.4918789785239</v>
       </c>
       <c r="D86">
-        <v>2.951242864506238</v>
+        <v>2.9276210214761</v>
       </c>
       <c r="E86">
-        <v>2.465199999999999</v>
+        <v>2.5405</v>
       </c>
       <c r="F86">
-        <v>6.325199999999999</v>
+        <v>6.400499999999999</v>
       </c>
       <c r="G86">
         <v>0.981</v>
@@ -8333,37 +8333,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M86">
-        <v>1.27010016</v>
+        <v>1.2852204</v>
       </c>
       <c r="N86">
-        <v>-0.5521001599999995</v>
+        <v>-0.5672203999999996</v>
       </c>
       <c r="O86">
-        <v>-0.08833602559999992</v>
+        <v>-0.09075526399999995</v>
       </c>
       <c r="P86">
-        <v>-0.4637641343999996</v>
+        <v>-0.4764651359999997</v>
       </c>
       <c r="Q86">
-        <v>-0.1667641343999996</v>
+        <v>-0.1794651359999997</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3296685956438599</v>
+        <v>0.3485931686867839</v>
       </c>
       <c r="T86">
-        <v>3.907558068591594</v>
+        <v>4.168061939831034</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.09044955950560628</v>
+        <v>0.08938544704083443</v>
       </c>
       <c r="W86">
-        <v>0.1826377284512743</v>
+        <v>0.1828514022342005</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5653097469100392</v>
+        <v>0.5586590440052153</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.207712667202088</v>
+        <v>0.209262667202088</v>
       </c>
       <c r="C87">
-        <v>-2.4918789785239</v>
+        <v>-2.590425684179403</v>
       </c>
       <c r="D87">
-        <v>2.9276210214761</v>
+        <v>2.904374315820597</v>
       </c>
       <c r="E87">
-        <v>2.5405</v>
+        <v>2.6158</v>
       </c>
       <c r="F87">
-        <v>6.400499999999999</v>
+        <v>6.4758</v>
       </c>
       <c r="G87">
         <v>0.981</v>
@@ -8415,37 +8415,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M87">
-        <v>1.2852204</v>
+        <v>1.30034064</v>
       </c>
       <c r="N87">
-        <v>-0.5672203999999996</v>
+        <v>-0.5823406399999997</v>
       </c>
       <c r="O87">
-        <v>-0.09075526399999995</v>
+        <v>-0.09317450239999996</v>
       </c>
       <c r="P87">
-        <v>-0.4764651359999997</v>
+        <v>-0.4891661375999998</v>
       </c>
       <c r="Q87">
-        <v>-0.1794651359999997</v>
+        <v>-0.1921661375999998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3485931686867839</v>
+        <v>0.3702212521644113</v>
       </c>
       <c r="T87">
-        <v>4.168061939831034</v>
+        <v>4.465780649818965</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.08938544704083443</v>
+        <v>0.08834608137756891</v>
       </c>
       <c r="W87">
-        <v>0.1828514022342005</v>
+        <v>0.1830601068593842</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5586590440052153</v>
+        <v>0.5521630086098057</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.209262667202088</v>
+        <v>0.210812667202088</v>
       </c>
       <c r="C88">
-        <v>-2.590425684179403</v>
+        <v>-2.688606118369149</v>
       </c>
       <c r="D88">
-        <v>2.904374315820597</v>
+        <v>2.88149388163085</v>
       </c>
       <c r="E88">
-        <v>2.6158</v>
+        <v>2.6911</v>
       </c>
       <c r="F88">
-        <v>6.4758</v>
+        <v>6.551099999999999</v>
       </c>
       <c r="G88">
         <v>0.981</v>
@@ -8497,37 +8497,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M88">
-        <v>1.30034064</v>
+        <v>1.31546088</v>
       </c>
       <c r="N88">
-        <v>-0.5823406399999997</v>
+        <v>-0.5974608799999996</v>
       </c>
       <c r="O88">
-        <v>-0.09317450239999996</v>
+        <v>-0.09559374079999994</v>
       </c>
       <c r="P88">
-        <v>-0.4891661375999998</v>
+        <v>-0.5018671391999997</v>
       </c>
       <c r="Q88">
-        <v>-0.1921661375999998</v>
+        <v>-0.2048671391999997</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3702212521644113</v>
+        <v>0.3951767331001352</v>
       </c>
       <c r="T88">
-        <v>4.465780649818965</v>
+        <v>4.809302238266578</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.08834608137756891</v>
+        <v>0.08733060917782674</v>
       </c>
       <c r="W88">
-        <v>0.1830601068593842</v>
+        <v>0.1832640136770924</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5521630086098057</v>
+        <v>0.5458163073614172</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.210812667202088</v>
+        <v>0.212362667202088</v>
       </c>
       <c r="C89">
-        <v>-2.688606118369149</v>
+        <v>-2.786428869805996</v>
       </c>
       <c r="D89">
-        <v>2.88149388163085</v>
+        <v>2.858971130194003</v>
       </c>
       <c r="E89">
-        <v>2.6911</v>
+        <v>2.7664</v>
       </c>
       <c r="F89">
-        <v>6.551099999999999</v>
+        <v>6.626399999999999</v>
       </c>
       <c r="G89">
         <v>0.981</v>
@@ -8579,37 +8579,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M89">
-        <v>1.31546088</v>
+        <v>1.33058112</v>
       </c>
       <c r="N89">
-        <v>-0.5974608799999996</v>
+        <v>-0.6125811199999998</v>
       </c>
       <c r="O89">
-        <v>-0.09559374079999994</v>
+        <v>-0.09801297919999996</v>
       </c>
       <c r="P89">
-        <v>-0.5018671391999997</v>
+        <v>-0.5145681407999998</v>
       </c>
       <c r="Q89">
-        <v>-0.2048671391999997</v>
+        <v>-0.2175681407999998</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3951767331001352</v>
+        <v>0.4242914608584799</v>
       </c>
       <c r="T89">
-        <v>4.809302238266578</v>
+        <v>5.210077424788794</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.08733060917782674</v>
+        <v>0.08633821589171507</v>
       </c>
       <c r="W89">
-        <v>0.1832640136770924</v>
+        <v>0.1834632862489436</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5458163073614172</v>
+        <v>0.5396138493232192</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.212362667202088</v>
+        <v>0.213912667202088</v>
       </c>
       <c r="C90">
-        <v>-2.786428869805996</v>
+        <v>-2.883902260756056</v>
       </c>
       <c r="D90">
-        <v>2.858971130194003</v>
+        <v>2.836797739243944</v>
       </c>
       <c r="E90">
-        <v>2.7664</v>
+        <v>2.8417</v>
       </c>
       <c r="F90">
-        <v>6.626399999999999</v>
+        <v>6.7017</v>
       </c>
       <c r="G90">
         <v>0.981</v>
@@ -8661,37 +8661,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M90">
-        <v>1.33058112</v>
+        <v>1.34570136</v>
       </c>
       <c r="N90">
-        <v>-0.6125811199999998</v>
+        <v>-0.6277013599999999</v>
       </c>
       <c r="O90">
-        <v>-0.09801297919999996</v>
+        <v>-0.1004322176</v>
       </c>
       <c r="P90">
-        <v>-0.5145681407999998</v>
+        <v>-0.5272691423999999</v>
       </c>
       <c r="Q90">
-        <v>-0.2175681407999998</v>
+        <v>-0.2302691423999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4242914608584799</v>
+        <v>0.4586997754819782</v>
       </c>
       <c r="T90">
-        <v>5.210077424788794</v>
+        <v>5.683720827042321</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.08633821589171507</v>
+        <v>0.085368123578325</v>
       </c>
       <c r="W90">
-        <v>0.1834632862489436</v>
+        <v>0.1836580807854724</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5396138493232192</v>
+        <v>0.5335507723645313</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.213912667202088</v>
+        <v>0.215462667202088</v>
       </c>
       <c r="C91">
-        <v>-2.883902260756056</v>
+        <v>-2.981034357291608</v>
       </c>
       <c r="D91">
-        <v>2.836797739243944</v>
+        <v>2.814965642708392</v>
       </c>
       <c r="E91">
-        <v>2.8417</v>
+        <v>2.917</v>
       </c>
       <c r="F91">
-        <v>6.7017</v>
+        <v>6.776999999999999</v>
       </c>
       <c r="G91">
         <v>0.981</v>
@@ -8743,37 +8743,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M91">
-        <v>1.34570136</v>
+        <v>1.3608216</v>
       </c>
       <c r="N91">
-        <v>-0.6277013599999999</v>
+        <v>-0.6428215999999998</v>
       </c>
       <c r="O91">
-        <v>-0.1004322176</v>
+        <v>-0.102851456</v>
       </c>
       <c r="P91">
-        <v>-0.5272691423999999</v>
+        <v>-0.5399701439999998</v>
       </c>
       <c r="Q91">
-        <v>-0.2302691423999999</v>
+        <v>-0.2429701439999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4586997754819782</v>
+        <v>0.4999897530301758</v>
       </c>
       <c r="T91">
-        <v>5.683720827042321</v>
+        <v>6.252092909746552</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.085368123578325</v>
+        <v>0.08441958887189918</v>
       </c>
       <c r="W91">
-        <v>0.1836580807854724</v>
+        <v>0.1838485465545227</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5335507723645313</v>
+        <v>0.5276224304493699</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.215462667202088</v>
+        <v>0.2170126672020879</v>
       </c>
       <c r="C92">
-        <v>-2.981034357291608</v>
+        <v>-3.077832979074206</v>
       </c>
       <c r="D92">
-        <v>2.814965642708392</v>
+        <v>2.793467020925793</v>
       </c>
       <c r="E92">
-        <v>2.917</v>
+        <v>2.9923</v>
       </c>
       <c r="F92">
-        <v>6.776999999999999</v>
+        <v>6.8523</v>
       </c>
       <c r="G92">
         <v>0.981</v>
@@ -8825,37 +8825,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M92">
-        <v>1.3608216</v>
+        <v>1.37594184</v>
       </c>
       <c r="N92">
-        <v>-0.6428215999999998</v>
+        <v>-0.6579418399999997</v>
       </c>
       <c r="O92">
-        <v>-0.102851456</v>
+        <v>-0.1052706943999999</v>
       </c>
       <c r="P92">
-        <v>-0.5399701439999998</v>
+        <v>-0.5526711455999997</v>
       </c>
       <c r="Q92">
-        <v>-0.2429701439999998</v>
+        <v>-0.2556711455999998</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4999897530301758</v>
+        <v>0.5504552811446398</v>
       </c>
       <c r="T92">
-        <v>6.252092909746552</v>
+        <v>6.946769899718392</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.08441958887189918</v>
+        <v>0.0834919010820981</v>
       </c>
       <c r="W92">
-        <v>0.1838485465545227</v>
+        <v>0.1840348262627147</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5276224304493699</v>
+        <v>0.5218243817631131</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2170126672020879</v>
+        <v>0.218562667202088</v>
       </c>
       <c r="C93">
-        <v>-3.077832979074206</v>
+        <v>-3.174305708692862</v>
       </c>
       <c r="D93">
-        <v>2.793467020925793</v>
+        <v>2.772294291307138</v>
       </c>
       <c r="E93">
-        <v>2.9923</v>
+        <v>3.067600000000001</v>
       </c>
       <c r="F93">
-        <v>6.8523</v>
+        <v>6.9276</v>
       </c>
       <c r="G93">
         <v>0.981</v>
@@ -8907,37 +8907,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M93">
-        <v>1.37594184</v>
+        <v>1.39106208</v>
       </c>
       <c r="N93">
-        <v>-0.6579418399999997</v>
+        <v>-0.6730620799999998</v>
       </c>
       <c r="O93">
-        <v>-0.1052706943999999</v>
+        <v>-0.1076899328</v>
       </c>
       <c r="P93">
-        <v>-0.5526711455999997</v>
+        <v>-0.5653721471999998</v>
       </c>
       <c r="Q93">
-        <v>-0.2556711455999998</v>
+        <v>-0.2683721471999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5504552811446398</v>
+        <v>0.61353719128772</v>
       </c>
       <c r="T93">
-        <v>6.946769899718392</v>
+        <v>7.815116137183193</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.0834919010820981</v>
+        <v>0.08258438041816224</v>
       </c>
       <c r="W93">
-        <v>0.1840348262627147</v>
+        <v>0.184217056412033</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5218243817631131</v>
+        <v>0.516152377613514</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.218562667202088</v>
+        <v>0.220112667202088</v>
       </c>
       <c r="C94">
-        <v>-3.174305708692862</v>
+        <v>-3.27045990058077</v>
       </c>
       <c r="D94">
-        <v>2.772294291307138</v>
+        <v>2.751440099419229</v>
       </c>
       <c r="E94">
-        <v>3.067600000000001</v>
+        <v>3.1429</v>
       </c>
       <c r="F94">
-        <v>6.9276</v>
+        <v>7.002899999999999</v>
       </c>
       <c r="G94">
         <v>0.981</v>
@@ -8989,37 +8989,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M94">
-        <v>1.39106208</v>
+        <v>1.40618232</v>
       </c>
       <c r="N94">
-        <v>-0.6730620799999998</v>
+        <v>-0.6881823199999997</v>
       </c>
       <c r="O94">
-        <v>-0.1076899328</v>
+        <v>-0.1101091712</v>
       </c>
       <c r="P94">
-        <v>-0.5653721471999998</v>
+        <v>-0.5780731487999997</v>
       </c>
       <c r="Q94">
-        <v>-0.2683721471999999</v>
+        <v>-0.2810731487999997</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.61353719128772</v>
+        <v>0.694642504328823</v>
       </c>
       <c r="T94">
-        <v>7.815116137183193</v>
+        <v>8.931561299637938</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.08258438041816224</v>
+        <v>0.08169637632764436</v>
       </c>
       <c r="W94">
-        <v>0.184217056412033</v>
+        <v>0.184395367633409</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.516152377613514</v>
+        <v>0.5106023520477774</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.220112667202088</v>
+        <v>0.221662667202088</v>
       </c>
       <c r="C95">
-        <v>-3.27045990058077</v>
+        <v>-3.366302689532591</v>
       </c>
       <c r="D95">
-        <v>2.751440099419229</v>
+        <v>2.730897310467409</v>
       </c>
       <c r="E95">
-        <v>3.1429</v>
+        <v>3.2182</v>
       </c>
       <c r="F95">
-        <v>7.002899999999999</v>
+        <v>7.0782</v>
       </c>
       <c r="G95">
         <v>0.981</v>
@@ -9071,37 +9071,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M95">
-        <v>1.40618232</v>
+        <v>1.42130256</v>
       </c>
       <c r="N95">
-        <v>-0.6881823199999997</v>
+        <v>-0.7033025599999998</v>
       </c>
       <c r="O95">
-        <v>-0.1101091712</v>
+        <v>-0.1125284096</v>
       </c>
       <c r="P95">
-        <v>-0.5780731487999997</v>
+        <v>-0.5907741503999998</v>
       </c>
       <c r="Q95">
-        <v>-0.2810731487999997</v>
+        <v>-0.2937741503999998</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.694642504328823</v>
+        <v>0.8027829217169604</v>
       </c>
       <c r="T95">
-        <v>8.931561299637938</v>
+        <v>10.4201548495776</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.08169637632764436</v>
+        <v>0.08082726594118006</v>
       </c>
       <c r="W95">
-        <v>0.184395367633409</v>
+        <v>0.1845698849990111</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5106023520477774</v>
+        <v>0.5051704121323755</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.221662667202088</v>
+        <v>0.2570169926701066</v>
       </c>
       <c r="C96">
-        <v>-3.366302689532591</v>
+        <v>-3.838994590330452</v>
       </c>
       <c r="D96">
-        <v>2.730897310467409</v>
+        <v>2.333505409669549</v>
       </c>
       <c r="E96">
-        <v>3.2182</v>
+        <v>3.293500000000001</v>
       </c>
       <c r="F96">
-        <v>7.0782</v>
+        <v>7.1535</v>
       </c>
       <c r="G96">
         <v>0.981</v>
@@ -9153,45 +9153,45 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M96">
-        <v>1.42130256</v>
+        <v>1.6867953</v>
       </c>
       <c r="N96">
-        <v>-0.7033025599999998</v>
+        <v>-0.9687953</v>
       </c>
       <c r="O96">
-        <v>-0.1125284096</v>
+        <v>-0.155007248</v>
       </c>
       <c r="P96">
-        <v>-0.5907741503999998</v>
+        <v>-0.813788052</v>
       </c>
       <c r="Q96">
-        <v>-0.2937741503999998</v>
+        <v>-0.5167880520000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8027829217169604</v>
+        <v>0.965266015420726</v>
       </c>
       <c r="T96">
-        <v>10.4201548495776</v>
+        <v>12.65679579385602</v>
       </c>
       <c r="U96">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08082726594118006</v>
+        <v>0.06810547788460165</v>
       </c>
       <c r="W96">
-        <v>0.1845698849990111</v>
+        <v>0.219740728314811</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.5051704121323755</v>
+        <v>0.4256592367787604</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2570169926701066</v>
+        <v>0.2589169926701066</v>
       </c>
       <c r="C97">
-        <v>-3.838994590330452</v>
+        <v>-3.932401752340742</v>
       </c>
       <c r="D97">
-        <v>2.333505409669549</v>
+        <v>2.315398247659258</v>
       </c>
       <c r="E97">
-        <v>3.293500000000001</v>
+        <v>3.3688</v>
       </c>
       <c r="F97">
-        <v>7.1535</v>
+        <v>7.2288</v>
       </c>
       <c r="G97">
         <v>0.981</v>
@@ -9235,37 +9235,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M97">
-        <v>1.6867953</v>
+        <v>1.70455104</v>
       </c>
       <c r="N97">
-        <v>-0.9687953</v>
+        <v>-0.9865510399999997</v>
       </c>
       <c r="O97">
-        <v>-0.155007248</v>
+        <v>-0.1578481664</v>
       </c>
       <c r="P97">
-        <v>-0.813788052</v>
+        <v>-0.8287028735999997</v>
       </c>
       <c r="Q97">
-        <v>-0.5167880520000001</v>
+        <v>-0.5317028735999998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.965266015420726</v>
+        <v>1.195132519275908</v>
       </c>
       <c r="T97">
-        <v>12.65679579385602</v>
+        <v>15.82099474232003</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06810547788460165</v>
+        <v>0.06739604582330373</v>
       </c>
       <c r="W97">
-        <v>0.219740728314811</v>
+        <v>0.219908012394865</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4256592367787604</v>
+        <v>0.4212252863956484</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2589169926701066</v>
+        <v>0.2608169926701066</v>
       </c>
       <c r="C98">
-        <v>-3.932401752340741</v>
+        <v>-4.02553006797981</v>
       </c>
       <c r="D98">
-        <v>2.315398247659258</v>
+        <v>2.29756993202019</v>
       </c>
       <c r="E98">
-        <v>3.368799999999999</v>
+        <v>3.4441</v>
       </c>
       <c r="F98">
-        <v>7.228799999999999</v>
+        <v>7.304099999999999</v>
       </c>
       <c r="G98">
         <v>0.981</v>
@@ -9317,37 +9317,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M98">
-        <v>1.70455104</v>
+        <v>1.72230678</v>
       </c>
       <c r="N98">
-        <v>-0.9865510399999995</v>
+        <v>-1.00430678</v>
       </c>
       <c r="O98">
-        <v>-0.1578481663999999</v>
+        <v>-0.1606890847999999</v>
       </c>
       <c r="P98">
-        <v>-0.8287028735999995</v>
+        <v>-0.8436176951999996</v>
       </c>
       <c r="Q98">
-        <v>-0.5317028735999996</v>
+        <v>-0.5466176951999997</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.195132519275905</v>
+        <v>1.57824335903454</v>
       </c>
       <c r="T98">
-        <v>15.82099474231999</v>
+        <v>21.09465965642666</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06739604582330375</v>
+        <v>0.06670124122718721</v>
       </c>
       <c r="W98">
-        <v>0.219908012394865</v>
+        <v>0.2200718473186292</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4212252863956484</v>
+        <v>0.41688275766992</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2608169926701066</v>
+        <v>0.2627169926701066</v>
       </c>
       <c r="C99">
-        <v>-4.02553006797981</v>
+        <v>-4.118385929290159</v>
       </c>
       <c r="D99">
-        <v>2.29756993202019</v>
+        <v>2.280014070709841</v>
       </c>
       <c r="E99">
-        <v>3.4441</v>
+        <v>3.5194</v>
       </c>
       <c r="F99">
-        <v>7.304099999999999</v>
+        <v>7.3794</v>
       </c>
       <c r="G99">
         <v>0.981</v>
@@ -9399,37 +9399,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M99">
-        <v>1.72230678</v>
+        <v>1.74006252</v>
       </c>
       <c r="N99">
-        <v>-1.00430678</v>
+        <v>-1.02206252</v>
       </c>
       <c r="O99">
-        <v>-0.1606890847999999</v>
+        <v>-0.1635300032</v>
       </c>
       <c r="P99">
-        <v>-0.8436176951999996</v>
+        <v>-0.8585325167999998</v>
       </c>
       <c r="Q99">
-        <v>-0.5466176951999997</v>
+        <v>-0.5615325167999998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.57824335903454</v>
+        <v>2.34446503855181</v>
       </c>
       <c r="T99">
-        <v>21.09465965642666</v>
+        <v>31.64198948463998</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06670124122718721</v>
+        <v>0.06602061631670571</v>
       </c>
       <c r="W99">
-        <v>0.2200718473186292</v>
+        <v>0.2202323386725208</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.41688275766992</v>
+        <v>0.4126288519794106</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2627169926701066</v>
+        <v>0.2646169926701066</v>
       </c>
       <c r="C100">
-        <v>-4.118385929290159</v>
+        <v>-4.210975534427961</v>
       </c>
       <c r="D100">
-        <v>2.280014070709841</v>
+        <v>2.262724465572038</v>
       </c>
       <c r="E100">
-        <v>3.5194</v>
+        <v>3.5947</v>
       </c>
       <c r="F100">
-        <v>7.3794</v>
+        <v>7.454699999999999</v>
       </c>
       <c r="G100">
         <v>0.981</v>
@@ -9481,37 +9481,37 @@
         <v>0.7180000000000002</v>
       </c>
       <c r="M100">
-        <v>1.74006252</v>
+        <v>1.75781826</v>
       </c>
       <c r="N100">
-        <v>-1.02206252</v>
+        <v>-1.03981826</v>
       </c>
       <c r="O100">
-        <v>-0.1635300032</v>
+        <v>-0.1663709215999999</v>
       </c>
       <c r="P100">
-        <v>-0.8585325167999998</v>
+        <v>-0.8734473383999997</v>
       </c>
       <c r="Q100">
-        <v>-0.5615325167999998</v>
+        <v>-0.5764473383999997</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.34446503855181</v>
+        <v>4.64313007710362</v>
       </c>
       <c r="T100">
-        <v>31.64198948463998</v>
+        <v>63.28397896927996</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06602061631670571</v>
+        <v>0.06535374140441574</v>
       </c>
       <c r="W100">
-        <v>0.2202323386725208</v>
+        <v>0.2203895877768388</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4126288519794106</v>
+        <v>0.4084608837775984</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2646169926701066</v>
-      </c>
-      <c r="C101">
-        <v>-4.210975534427961</v>
-      </c>
-      <c r="D101">
-        <v>2.262724465572038</v>
-      </c>
-      <c r="E101">
-        <v>3.5947</v>
-      </c>
-      <c r="F101">
-        <v>7.454699999999999</v>
-      </c>
-      <c r="G101">
-        <v>0.981</v>
-      </c>
-      <c r="H101">
-        <v>3.67</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.015</v>
-      </c>
-      <c r="K101">
-        <v>0.297</v>
-      </c>
-      <c r="L101">
-        <v>0.7180000000000002</v>
-      </c>
-      <c r="M101">
-        <v>1.75781826</v>
-      </c>
-      <c r="N101">
-        <v>-1.03981826</v>
-      </c>
-      <c r="O101">
-        <v>-0.1663709215999999</v>
-      </c>
-      <c r="P101">
-        <v>-0.8734473383999997</v>
-      </c>
-      <c r="Q101">
-        <v>-0.5764473383999997</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.64313007710362</v>
-      </c>
-      <c r="T101">
-        <v>63.28397896927996</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06535374140441574</v>
-      </c>
-      <c r="W101">
-        <v>0.2203895877768388</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4084608837775984</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
